--- a/InputData/fuels/BFPIaE/BAU Fuel Production Imports and Exports.xlsx
+++ b/InputData/fuels/BFPIaE/BAU Fuel Production Imports and Exports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250507_FINAL/Precios/BFPIaE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\fuels\BFPIaE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA1FD14-AC90-FA4B-9FDB-2CA0B609D7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB66E3D-32EA-4A1F-AF0C-E200A596B3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" tabRatio="684" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37515" yWindow="750" windowWidth="20565" windowHeight="13815" tabRatio="684" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -1218,7 +1218,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="787">
   <si>
     <t>BFPIaE BAU Fuel Production</t>
   </si>
@@ -3573,6 +3573,12 @@
   </si>
   <si>
     <t>heat (energy carrier)</t>
+  </si>
+  <si>
+    <t>National Energy Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gob.mx/sener/articulos/balance-nacional-de-energia-296106 </t>
   </si>
 </sst>
 </file>
@@ -3595,7 +3601,7 @@
     <numFmt numFmtId="175" formatCode="#,##0.0000000"/>
     <numFmt numFmtId="176" formatCode="0.0000E+00"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3800,7 +3806,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3942,6 +3948,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4247,7 +4259,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4710,14 +4722,16 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="8" applyFont="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="Body: normal cell" xfId="7" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4761,57 +4775,9 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
-      <sheetName val="MEX Urban vs. Rural"/>
-      <sheetName val="BCEU_consumoPJ"/>
-      <sheetName val="BCEU_consumoBTU"/>
-      <sheetName val="Electricity GR"/>
-      <sheetName val="NG &amp; Biomass GR"/>
-      <sheetName val="Diesel GR"/>
-      <sheetName val="Heat GR"/>
-      <sheetName val="BNE Fuel &amp; component splits"/>
-      <sheetName val="BCEU-urban-residential-heating"/>
-      <sheetName val="BCEU-urban-residential-cooling"/>
-      <sheetName val="BCEU-urban-residential-lighting"/>
-      <sheetName val="BCEU-urban-residential-appl"/>
-      <sheetName val="BCEU-urban-residential-other"/>
-      <sheetName val="BCEU-rural-residential-heating"/>
-      <sheetName val="BCEU-rural-residential-cooling"/>
-      <sheetName val="BCEU-rural-residential-lighting"/>
-      <sheetName val="BCEU-rural-residential-appl"/>
-      <sheetName val="BCEU-rural-residential-other"/>
-      <sheetName val="BCEU-commercial-heating"/>
-      <sheetName val="BCEU-commercial-cooling"/>
-      <sheetName val="BCEU-commercial-lighting"/>
-      <sheetName val="BCEU-commercial-appl"/>
-      <sheetName val="BCEU-commercial-other"/>
-      <sheetName val="BCEU-all-envelope"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5158,472 +5124,499 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B107"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:F107"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="82.7109375" customWidth="1"/>
+    <col min="2" max="2" width="82.6640625" customWidth="1"/>
+    <col min="6" max="6" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="F5" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="F6" s="219" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>2019</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="F7" s="219" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="F8" s="219" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="F9" s="219" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="F10" s="219" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F11" s="219" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="F12" s="4" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>2018</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="3">
         <v>2016</v>
       </c>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="2:2">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="2:2">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:2">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="2:2">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" s="3">
         <v>2018</v>
       </c>
     </row>
-    <row r="57" spans="2:2">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="2:2">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="2:2">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" s="4"/>
     </row>
-    <row r="60" spans="2:2">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="2:2">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="2:2">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B62" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="63" spans="2:2">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="2:2">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64" s="193" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B67" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B69" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B74" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B76" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B79" s="198"/>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>76</v>
       </c>
@@ -5640,9 +5633,10 @@
     <hyperlink ref="B52" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="B58" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="B78" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{56C9DA41-C3F4-4E41-BFF7-6F7018B80F81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
 
@@ -5652,19 +5646,19 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.42578125" customWidth="1"/>
-    <col min="2" max="4" width="13.42578125" style="18" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="18" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="4" width="13.44140625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.95">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>454</v>
       </c>
@@ -5687,7 +5681,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.95">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>751</v>
       </c>
@@ -5697,7 +5691,7 @@
       <c r="E2" s="29"/>
       <c r="F2" s="30"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>752</v>
       </c>
@@ -5721,31 +5715,31 @@
         <v>753</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>754</v>
       </c>
       <c r="B4" s="22">
-        <f>OrigenDestino_2019!E11+OrigenDestino_2019!W42</f>
-        <v>2466.9690000000001</v>
+        <f>OrigenDestino_2019!E11</f>
+        <v>1466.0360000000001</v>
       </c>
       <c r="C4" s="22">
-        <f>OrigenDestino_2019!E13+OrigenDestino_2019!W13</f>
-        <v>2213.002</v>
+        <f>OrigenDestino_2019!E13</f>
+        <v>0</v>
       </c>
       <c r="D4" s="22">
-        <f>-(OrigenDestino_2019!E16+OrigenDestino_2019!W16)</f>
-        <v>1.403</v>
+        <f>-(OrigenDestino_2019!E16)</f>
+        <v>0</v>
       </c>
       <c r="E4" s="23">
         <f t="shared" ref="E4:E5" si="0">B4+C4-D4</f>
-        <v>4678.5679999999993</v>
+        <v>1466.0360000000001</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>755</v>
       </c>
@@ -5769,7 +5763,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>756</v>
       </c>
@@ -5779,7 +5773,7 @@
       <c r="E6" s="29"/>
       <c r="F6" s="30"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>757</v>
       </c>
@@ -5789,7 +5783,7 @@
       <c r="E7" s="29"/>
       <c r="F7" s="30"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>758</v>
       </c>
@@ -5799,7 +5793,7 @@
       <c r="E8" s="29"/>
       <c r="F8" s="30"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>759</v>
       </c>
@@ -5823,7 +5817,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>760</v>
       </c>
@@ -5847,7 +5841,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>761</v>
       </c>
@@ -5871,7 +5865,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>762</v>
       </c>
@@ -5892,7 +5886,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>763</v>
       </c>
@@ -5913,7 +5907,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>764</v>
       </c>
@@ -5937,7 +5931,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>765</v>
       </c>
@@ -5947,7 +5941,7 @@
       <c r="E15" s="29"/>
       <c r="F15" s="30"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>766</v>
       </c>
@@ -5957,7 +5951,7 @@
       <c r="E16" s="29"/>
       <c r="F16" s="30"/>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>767</v>
       </c>
@@ -5978,7 +5972,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>768</v>
       </c>
@@ -6002,7 +5996,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>769</v>
       </c>
@@ -6026,7 +6020,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>770</v>
       </c>
@@ -6050,7 +6044,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>771</v>
       </c>
@@ -6072,7 +6066,7 @@
       </c>
       <c r="I21" s="194"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>772</v>
       </c>
@@ -6093,7 +6087,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="188" t="s">
         <v>773</v>
       </c>
@@ -6103,7 +6097,7 @@
       <c r="E24" s="189"/>
       <c r="F24" s="190"/>
     </row>
-    <row r="25" spans="1:12" ht="15.95">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="32" t="s">
         <v>454</v>
       </c>
@@ -6128,7 +6122,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:12" ht="15.95">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="31" t="s">
         <v>751</v>
       </c>
@@ -6144,7 +6138,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>752</v>
       </c>
@@ -6184,25 +6178,25 @@
         <v>778</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>754</v>
       </c>
       <c r="B28" s="191">
-        <f t="shared" ref="B28:E29" si="4">B4*$H28</f>
-        <v>2338235452709280</v>
+        <f>B4*$H28</f>
+        <v>1389534019336320</v>
       </c>
       <c r="C28" s="191">
-        <f t="shared" si="4"/>
-        <v>2097521182194240</v>
+        <f t="shared" ref="B28:E29" si="4">C4*$H28</f>
+        <v>0</v>
       </c>
       <c r="D28" s="191">
         <f t="shared" si="4"/>
-        <v>1329787419360</v>
+        <v>0</v>
       </c>
       <c r="E28" s="191">
         <f t="shared" si="4"/>
-        <v>4434426847484159.5</v>
+        <v>1389534019336320</v>
       </c>
       <c r="F28" t="s">
         <v>631</v>
@@ -6220,7 +6214,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>755</v>
       </c>
@@ -6256,7 +6250,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>756</v>
       </c>
@@ -6278,7 +6272,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>757</v>
       </c>
@@ -6300,7 +6294,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>758</v>
       </c>
@@ -6322,7 +6316,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>759</v>
       </c>
@@ -6358,7 +6352,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>760</v>
       </c>
@@ -6394,7 +6388,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>761</v>
       </c>
@@ -6430,7 +6424,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>762</v>
       </c>
@@ -6466,7 +6460,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>763</v>
       </c>
@@ -6502,7 +6496,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>764</v>
       </c>
@@ -6538,7 +6532,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>765</v>
       </c>
@@ -6560,7 +6554,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>766</v>
       </c>
@@ -6582,7 +6576,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>767</v>
       </c>
@@ -6618,7 +6612,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>768</v>
       </c>
@@ -6654,7 +6648,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>769</v>
       </c>
@@ -6690,7 +6684,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>770</v>
       </c>
@@ -6726,7 +6720,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>771</v>
       </c>
@@ -6762,7 +6756,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>772</v>
       </c>
@@ -6809,13 +6803,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AI73"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.85546875" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="196" t="s">
         <v>779</v>
       </c>
@@ -6854,7 +6848,7 @@
       <c r="AH1" s="197"/>
       <c r="AI1" s="197"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1">
+    <row r="2" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>2019</v>
       </c>
@@ -6952,7 +6946,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="15.95">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>751</v>
       </c>
@@ -7055,7 +7049,7 @@
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>752</v>
       </c>
@@ -7188,7 +7182,7 @@
         <v>0.6213817051655971</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>754</v>
       </c>
@@ -7321,7 +7315,7 @@
         <v>1.5783559488591974</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>755</v>
       </c>
@@ -7454,7 +7448,7 @@
         <v>0.46585691775301491</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>756</v>
       </c>
@@ -7557,7 +7551,7 @@
       <c r="AH7" s="7"/>
       <c r="AI7" s="7"/>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>757</v>
       </c>
@@ -7660,7 +7654,7 @@
       <c r="AH8" s="7"/>
       <c r="AI8" s="7"/>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>758</v>
       </c>
@@ -7763,7 +7757,7 @@
       <c r="AH9" s="7"/>
       <c r="AI9" s="7"/>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>759</v>
       </c>
@@ -7896,7 +7890,7 @@
         <v>1.1603109106810525</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>760</v>
       </c>
@@ -8029,7 +8023,7 @@
         <v>1.5448237358492658</v>
       </c>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>761</v>
       </c>
@@ -8162,7 +8156,7 @@
         <v>1.5448237358492658</v>
       </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>762</v>
       </c>
@@ -8295,7 +8289,7 @@
         <v>1.1603109106810525</v>
       </c>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>763</v>
       </c>
@@ -8428,7 +8422,7 @@
         <v>1.1603109106810525</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>764</v>
       </c>
@@ -8561,7 +8555,7 @@
         <v>1.5448237358492658</v>
       </c>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>765</v>
       </c>
@@ -8664,7 +8658,7 @@
       <c r="AH16" s="7"/>
       <c r="AI16" s="7"/>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>766</v>
       </c>
@@ -8767,7 +8761,7 @@
       <c r="AH17" s="7"/>
       <c r="AI17" s="7"/>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>767</v>
       </c>
@@ -8900,7 +8894,7 @@
         <v>0.6213817051655971</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>768</v>
       </c>
@@ -9033,7 +9027,7 @@
         <v>1.5448237358492658</v>
       </c>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>769</v>
       </c>
@@ -9166,7 +9160,7 @@
         <v>1.5448237358492658</v>
       </c>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>770</v>
       </c>
@@ -9299,7 +9293,7 @@
         <v>1.5985688669719726</v>
       </c>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>771</v>
       </c>
@@ -9432,7 +9426,7 @@
         <v>0.43188132656901734</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>772</v>
       </c>
@@ -9533,7 +9527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="196" t="s">
         <v>780</v>
       </c>
@@ -9572,7 +9566,7 @@
       <c r="AH26" s="197"/>
       <c r="AI26" s="197"/>
     </row>
-    <row r="27" spans="1:35" s="1" customFormat="1">
+    <row r="27" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <f>B2</f>
         <v>2019</v>
@@ -9702,7 +9696,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="15.95">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="31" t="s">
         <v>751</v>
       </c>
@@ -9805,7 +9799,7 @@
       <c r="AH28" s="7"/>
       <c r="AI28" s="7"/>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>752</v>
       </c>
@@ -9938,7 +9932,7 @@
         <v>0.65656368206805971</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>754</v>
       </c>
@@ -10071,7 +10065,7 @@
         <v>0.39633581386350036</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>755</v>
       </c>
@@ -10172,7 +10166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>756</v>
       </c>
@@ -10275,7 +10269,7 @@
       <c r="AH32" s="7"/>
       <c r="AI32" s="7"/>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>757</v>
       </c>
@@ -10378,7 +10372,7 @@
       <c r="AH33" s="7"/>
       <c r="AI33" s="7"/>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>758</v>
       </c>
@@ -10481,7 +10475,7 @@
       <c r="AH34" s="7"/>
       <c r="AI34" s="7"/>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>759</v>
       </c>
@@ -10582,7 +10576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>760</v>
       </c>
@@ -10715,7 +10709,7 @@
         <v>0.76637959961128599</v>
       </c>
     </row>
-    <row r="37" spans="1:35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>761</v>
       </c>
@@ -10848,7 +10842,7 @@
         <v>0.76637959961128599</v>
       </c>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>762</v>
       </c>
@@ -10981,7 +10975,7 @@
         <v>0.76637959961128599</v>
       </c>
     </row>
-    <row r="39" spans="1:35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>763</v>
       </c>
@@ -11114,7 +11108,7 @@
         <v>0.76637959961128599</v>
       </c>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>764</v>
       </c>
@@ -11247,7 +11241,7 @@
         <v>0.76637959961128599</v>
       </c>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>765</v>
       </c>
@@ -11350,7 +11344,7 @@
       <c r="AH41" s="7"/>
       <c r="AI41" s="7"/>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>766</v>
       </c>
@@ -11453,7 +11447,7 @@
       <c r="AH42" s="7"/>
       <c r="AI42" s="7"/>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>767</v>
       </c>
@@ -11586,7 +11580,7 @@
         <v>0.65656368206805971</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>768</v>
       </c>
@@ -11719,7 +11713,7 @@
         <v>0.37719731431844361</v>
       </c>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>769</v>
       </c>
@@ -11852,7 +11846,7 @@
         <v>0.76637959961128599</v>
       </c>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>770</v>
       </c>
@@ -11985,7 +11979,7 @@
         <v>0.76637959961128599</v>
       </c>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>771</v>
       </c>
@@ -12086,7 +12080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>772</v>
       </c>
@@ -12187,7 +12181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="196" t="s">
         <v>781</v>
       </c>
@@ -12226,7 +12220,7 @@
       <c r="AH51" s="197"/>
       <c r="AI51" s="197"/>
     </row>
-    <row r="52" spans="1:35" s="1" customFormat="1">
+    <row r="52" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1">
         <f>B2</f>
         <v>2019</v>
@@ -12356,7 +12350,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="15.95">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="31" t="s">
         <v>751</v>
       </c>
@@ -12459,7 +12453,7 @@
       <c r="AH53" s="7"/>
       <c r="AI53" s="7"/>
     </row>
-    <row r="54" spans="1:35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>752</v>
       </c>
@@ -12592,7 +12586,7 @@
         <v>1.134402445441947</v>
       </c>
     </row>
-    <row r="55" spans="1:35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>754</v>
       </c>
@@ -12725,7 +12719,7 @@
         <v>2.6863800598260537</v>
       </c>
     </row>
-    <row r="56" spans="1:35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>755</v>
       </c>
@@ -12826,7 +12820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>756</v>
       </c>
@@ -12929,7 +12923,7 @@
       <c r="AH57" s="7"/>
       <c r="AI57" s="7"/>
     </row>
-    <row r="58" spans="1:35">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>757</v>
       </c>
@@ -13032,7 +13026,7 @@
       <c r="AH58" s="7"/>
       <c r="AI58" s="7"/>
     </row>
-    <row r="59" spans="1:35">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>758</v>
       </c>
@@ -13135,7 +13129,7 @@
       <c r="AH59" s="7"/>
       <c r="AI59" s="7"/>
     </row>
-    <row r="60" spans="1:35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>759</v>
       </c>
@@ -13236,7 +13230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>760</v>
       </c>
@@ -13369,7 +13363,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="62" spans="1:35">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>761</v>
       </c>
@@ -13502,7 +13496,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="63" spans="1:35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>762</v>
       </c>
@@ -13635,7 +13629,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="64" spans="1:35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>763</v>
       </c>
@@ -13768,7 +13762,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="65" spans="1:35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>764</v>
       </c>
@@ -13901,7 +13895,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="66" spans="1:35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>765</v>
       </c>
@@ -14004,7 +13998,7 @@
       <c r="AH66" s="7"/>
       <c r="AI66" s="7"/>
     </row>
-    <row r="67" spans="1:35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>766</v>
       </c>
@@ -14107,7 +14101,7 @@
       <c r="AH67" s="7"/>
       <c r="AI67" s="7"/>
     </row>
-    <row r="68" spans="1:35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>767</v>
       </c>
@@ -14240,7 +14234,7 @@
         <v>1.134402445441947</v>
       </c>
     </row>
-    <row r="69" spans="1:35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>768</v>
       </c>
@@ -14373,7 +14367,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="70" spans="1:35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>769</v>
       </c>
@@ -14506,7 +14500,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="71" spans="1:35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>770</v>
       </c>
@@ -14639,7 +14633,7 @@
         <v>1.4092271355100565</v>
       </c>
     </row>
-    <row r="72" spans="1:35">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>771</v>
       </c>
@@ -14740,7 +14734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:35">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>772</v>
       </c>
@@ -14852,14 +14846,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:BA22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
     <col min="2" max="35" width="13" customWidth="1"/>
-    <col min="36" max="53" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="53" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="15.95">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>782</v>
       </c>
@@ -15020,7 +15014,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="15.95">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>751</v>
       </c>
@@ -15233,7 +15227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>752</v>
       </c>
@@ -15446,220 +15440,220 @@
         <v>175080192899944.69</v>
       </c>
     </row>
-    <row r="4" spans="1:53">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:53" s="237" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="236" t="s">
         <v>754</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="237">
         <f>'Start Year Data'!B28</f>
-        <v>2338235452709280</v>
-      </c>
-      <c r="C4">
+        <v>1389534019336320</v>
+      </c>
+      <c r="C4" s="237">
         <f>$B4*'Time Series Scaling Factors'!C5</f>
-        <v>2388195390467183</v>
-      </c>
-      <c r="D4">
+        <v>1419223515763249.3</v>
+      </c>
+      <c r="D4" s="237">
         <f>$B4*'Time Series Scaling Factors'!D5</f>
-        <v>2515112993845854</v>
-      </c>
-      <c r="E4">
+        <v>1494646342554689.8</v>
+      </c>
+      <c r="E4" s="237">
         <f>$B4*'Time Series Scaling Factors'!E5</f>
-        <v>2558658821235072.5</v>
-      </c>
-      <c r="F4">
+        <v>1520524150748623.3</v>
+      </c>
+      <c r="F4" s="237">
         <f>$B4*'Time Series Scaling Factors'!F5</f>
-        <v>2589877625437556.5</v>
-      </c>
-      <c r="G4">
+        <v>1539076427180874</v>
+      </c>
+      <c r="G4" s="237">
         <f>$B4*'Time Series Scaling Factors'!G5</f>
-        <v>2632199671457709</v>
-      </c>
-      <c r="H4">
+        <v>1564226983616402.8</v>
+      </c>
+      <c r="H4" s="237">
         <f>$B4*'Time Series Scaling Factors'!H5</f>
-        <v>2724417138823404.5</v>
-      </c>
-      <c r="I4">
+        <v>1619028696563316.8</v>
+      </c>
+      <c r="I4" s="237">
         <f>$B4*'Time Series Scaling Factors'!I5</f>
-        <v>2815917065785647</v>
-      </c>
-      <c r="J4">
+        <v>1673403999586588.5</v>
+      </c>
+      <c r="J4" s="237">
         <f>$B4*'Time Series Scaling Factors'!J5</f>
-        <v>2871285181870589</v>
-      </c>
-      <c r="K4">
+        <v>1706307392954200.5</v>
+      </c>
+      <c r="K4" s="237">
         <f>$B4*'Time Series Scaling Factors'!K5</f>
-        <v>2926038197825104</v>
-      </c>
-      <c r="L4">
+        <v>1738845253177775.8</v>
+      </c>
+      <c r="L4" s="237">
         <f>$B4*'Time Series Scaling Factors'!L5</f>
-        <v>2964850223518406</v>
-      </c>
-      <c r="M4">
+        <v>1761909923588837.3</v>
+      </c>
+      <c r="M4" s="237">
         <f>$B4*'Time Series Scaling Factors'!M5</f>
-        <v>2985300092267369.5</v>
-      </c>
-      <c r="N4">
+        <v>1774062586950742.3</v>
+      </c>
+      <c r="N4" s="237">
         <f>$B4*'Time Series Scaling Factors'!N5</f>
-        <v>3017286740025278.5</v>
-      </c>
-      <c r="O4">
+        <v>1793071166763627.5</v>
+      </c>
+      <c r="O4" s="237">
         <f>$B4*'Time Series Scaling Factors'!O5</f>
-        <v>3059296683806960</v>
-      </c>
-      <c r="P4">
+        <v>1818036251424975.5</v>
+      </c>
+      <c r="P4" s="237">
         <f>$B4*'Time Series Scaling Factors'!P5</f>
-        <v>3103136339242721.5</v>
-      </c>
-      <c r="Q4">
+        <v>1844088671660666.5</v>
+      </c>
+      <c r="Q4" s="237">
         <f>$B4*'Time Series Scaling Factors'!Q5</f>
-        <v>3139070539951403.5</v>
-      </c>
-      <c r="R4">
+        <v>1865443148295822</v>
+      </c>
+      <c r="R4" s="237">
         <f>$B4*'Time Series Scaling Factors'!R5</f>
-        <v>3171922624619475</v>
-      </c>
-      <c r="S4">
+        <v>1884966027909810</v>
+      </c>
+      <c r="S4" s="237">
         <f>$B4*'Time Series Scaling Factors'!S5</f>
-        <v>3225737172395014.5</v>
-      </c>
-      <c r="T4">
+        <v>1916946188326362.3</v>
+      </c>
+      <c r="T4" s="237">
         <f>$B4*'Time Series Scaling Factors'!T5</f>
-        <v>3249897226096383</v>
-      </c>
-      <c r="U4">
+        <v>1931303688760352</v>
+      </c>
+      <c r="U4" s="237">
         <f>$B4*'Time Series Scaling Factors'!U5</f>
-        <v>3292921878771746.5</v>
-      </c>
-      <c r="V4">
+        <v>1956871780499477.8</v>
+      </c>
+      <c r="V4" s="237">
         <f>$B4*'Time Series Scaling Factors'!V5</f>
-        <v>3326605995913124</v>
-      </c>
-      <c r="W4">
+        <v>1976889108790784.3</v>
+      </c>
+      <c r="W4" s="237">
         <f>$B4*'Time Series Scaling Factors'!W5</f>
-        <v>3362017973925618</v>
-      </c>
-      <c r="X4">
+        <v>1997933246190778</v>
+      </c>
+      <c r="X4" s="237">
         <f>$B4*'Time Series Scaling Factors'!X5</f>
-        <v>3392860224976167</v>
-      </c>
-      <c r="Y4">
+        <v>2016261749857075.8</v>
+      </c>
+      <c r="Y4" s="237">
         <f>$B4*'Time Series Scaling Factors'!Y5</f>
-        <v>3425291610236536</v>
-      </c>
-      <c r="Z4">
+        <v>2035534622082697.5</v>
+      </c>
+      <c r="Z4" s="237">
         <f>$B4*'Time Series Scaling Factors'!Z5</f>
-        <v>3455350559992253</v>
-      </c>
-      <c r="AA4">
+        <v>2053397636358139.3</v>
+      </c>
+      <c r="AA4" s="237">
         <f>$B4*'Time Series Scaling Factors'!AA5</f>
-        <v>3489965481941797</v>
-      </c>
-      <c r="AB4">
+        <v>2073968110375130</v>
+      </c>
+      <c r="AB4" s="237">
         <f>$B4*'Time Series Scaling Factors'!AB5</f>
-        <v>3518532563347951.5</v>
-      </c>
-      <c r="AC4">
+        <v>2090944557892854.5</v>
+      </c>
+      <c r="AC4" s="237">
         <f>$B4*'Time Series Scaling Factors'!AC5</f>
-        <v>3559496817258238</v>
-      </c>
-      <c r="AD4">
+        <v>2115288224532208.5</v>
+      </c>
+      <c r="AD4" s="237">
         <f>$B4*'Time Series Scaling Factors'!AD5</f>
-        <v>3590189730826370.5</v>
-      </c>
-      <c r="AE4">
+        <v>2133527981998058.8</v>
+      </c>
+      <c r="AE4" s="237">
         <f>$B4*'Time Series Scaling Factors'!AE5</f>
-        <v>3622174610114093</v>
-      </c>
-      <c r="AF4">
+        <v>2152535510869096.8</v>
+      </c>
+      <c r="AF4" s="237">
         <f>$B4*'Time Series Scaling Factors'!AF5</f>
-        <v>3654826333659922.5</v>
-      </c>
-      <c r="AG4">
+        <v>2171939322664151</v>
+      </c>
+      <c r="AG4" s="237">
         <f>$B4*'Time Series Scaling Factors'!AG5</f>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AH4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AH4" s="237">
         <f t="shared" ref="AH4:BA4" si="2">AG4</f>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AI4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AI4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AJ4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AJ4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AK4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AK4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AL4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AL4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AM4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AM4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AN4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AN4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AO4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AO4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AP4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AP4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AQ4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AQ4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AR4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AR4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AS4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AS4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AT4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AT4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AU4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AU4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AV4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AV4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AW4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AW4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AX4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AX4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AY4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AY4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="AZ4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="AZ4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-      <c r="BA4">
+        <v>2193179285561711.8</v>
+      </c>
+      <c r="BA4" s="237">
         <f t="shared" si="2"/>
-        <v>3690567836617170.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:53">
+        <v>2193179285561711.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>783</v>
       </c>
@@ -15872,7 +15866,7 @@
         <v>55112592133925.07</v>
       </c>
     </row>
-    <row r="6" spans="1:53">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>756</v>
       </c>
@@ -16085,7 +16079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>757</v>
       </c>
@@ -16298,7 +16292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>758</v>
       </c>
@@ -16511,7 +16505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>759</v>
       </c>
@@ -16724,7 +16718,7 @@
         <v>397199039093203.5</v>
       </c>
     </row>
-    <row r="10" spans="1:53">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>760</v>
       </c>
@@ -16937,7 +16931,7 @@
         <v>696926073418869.25</v>
       </c>
     </row>
-    <row r="11" spans="1:53">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>761</v>
       </c>
@@ -17150,7 +17144,7 @@
         <v>321963757175815.75</v>
       </c>
     </row>
-    <row r="12" spans="1:53">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>762</v>
       </c>
@@ -17363,7 +17357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>763</v>
       </c>
@@ -17576,7 +17570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>764</v>
       </c>
@@ -17789,7 +17783,7 @@
         <v>89174805030168.438</v>
       </c>
     </row>
-    <row r="15" spans="1:53">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>765</v>
       </c>
@@ -18002,7 +17996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:53">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>766</v>
       </c>
@@ -18215,7 +18209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>767</v>
       </c>
@@ -18428,7 +18422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>768</v>
       </c>
@@ -18641,7 +18635,7 @@
         <v>5547367494282751</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>769</v>
       </c>
@@ -18854,7 +18848,7 @@
         <v>518589641251990.31</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>770</v>
       </c>
@@ -19067,7 +19061,7 @@
         <v>246328694309794.06</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>771</v>
       </c>
@@ -19280,7 +19274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>772</v>
       </c>
@@ -19505,14 +19499,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:BA22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
     <col min="2" max="35" width="13" customWidth="1"/>
-    <col min="36" max="53" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="53" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="15.95">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>782</v>
       </c>
@@ -19673,7 +19667,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="15.95">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>751</v>
       </c>
@@ -19886,7 +19880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>752</v>
       </c>
@@ -20099,220 +20093,220 @@
         <v>264269383177389.5</v>
       </c>
     </row>
-    <row r="4" spans="1:53">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>754</v>
       </c>
       <c r="B4">
         <f>'Start Year Data'!C28</f>
-        <v>2097521182194240</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f>$B4*'Time Series Scaling Factors'!C30</f>
-        <v>2045418890398790</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f>$B4*'Time Series Scaling Factors'!D30</f>
-        <v>1802080972054882.3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>$B4*'Time Series Scaling Factors'!E30</f>
-        <v>1736635593704864</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <f>$B4*'Time Series Scaling Factors'!F30</f>
-        <v>1657431542944762.3</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <f>$B4*'Time Series Scaling Factors'!G30</f>
-        <v>1631562262828293.8</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <f>$B4*'Time Series Scaling Factors'!H30</f>
-        <v>1691698963993210.8</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <f>$B4*'Time Series Scaling Factors'!I30</f>
-        <v>1761827010454831.8</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <f>$B4*'Time Series Scaling Factors'!J30</f>
-        <v>1645299141405086</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <f>$B4*'Time Series Scaling Factors'!K30</f>
-        <v>1425949469911182.3</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f>$B4*'Time Series Scaling Factors'!L30</f>
-        <v>1362723304999386.5</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <f>$B4*'Time Series Scaling Factors'!M30</f>
-        <v>1330164069574060</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <f>$B4*'Time Series Scaling Factors'!N30</f>
-        <v>1382633850489486.8</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <f>$B4*'Time Series Scaling Factors'!O30</f>
-        <v>1327506724935538.3</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f>$B4*'Time Series Scaling Factors'!P30</f>
-        <v>1199569408402184.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <f>$B4*'Time Series Scaling Factors'!Q30</f>
-        <v>1170747439630526</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <f>$B4*'Time Series Scaling Factors'!R30</f>
-        <v>1144058260475418.3</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f>$B4*'Time Series Scaling Factors'!S30</f>
-        <v>1128698868585682.3</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <f>$B4*'Time Series Scaling Factors'!T30</f>
-        <v>1131055608627086.3</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <f>$B4*'Time Series Scaling Factors'!U30</f>
-        <v>1116974537786593.6</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <f>$B4*'Time Series Scaling Factors'!V30</f>
-        <v>1100934276484385.6</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <f>$B4*'Time Series Scaling Factors'!W30</f>
-        <v>1084703131263007.8</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <f>$B4*'Time Series Scaling Factors'!X30</f>
-        <v>1078951062297157.8</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <f>$B4*'Time Series Scaling Factors'!Y30</f>
-        <v>1048196205966031.3</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <f>$B4*'Time Series Scaling Factors'!Z30</f>
-        <v>1008027165164666.9</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <f>$B4*'Time Series Scaling Factors'!AA30</f>
-        <v>968893707200373.38</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <f>$B4*'Time Series Scaling Factors'!AB30</f>
-        <v>949641485777961.13</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f>$B4*'Time Series Scaling Factors'!AC30</f>
-        <v>918985077452390.88</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <f>$B4*'Time Series Scaling Factors'!AD30</f>
-        <v>889622771917412.75</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <f>$B4*'Time Series Scaling Factors'!AE30</f>
-        <v>865125751786787</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <f>$B4*'Time Series Scaling Factors'!AF30</f>
-        <v>855599592104122.63</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <f>$B4*'Time Series Scaling Factors'!AG30</f>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <f t="shared" ref="AH4:BA4" si="2">AG4</f>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AI4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AM4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AN4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AP4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AR4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AS4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AT4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AU4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AV4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AW4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AX4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AY4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="AZ4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
+        <v>0</v>
       </c>
       <c r="BA4">
         <f t="shared" si="2"/>
-        <v>831322764840885.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>783</v>
       </c>
@@ -20525,7 +20519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>756</v>
       </c>
@@ -20738,7 +20732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>757</v>
       </c>
@@ -20951,7 +20945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>758</v>
       </c>
@@ -21164,7 +21158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>759</v>
       </c>
@@ -21377,7 +21371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>760</v>
       </c>
@@ -21590,7 +21584,7 @@
         <v>819427074116322.5</v>
       </c>
     </row>
-    <row r="11" spans="1:53">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>761</v>
       </c>
@@ -21803,7 +21797,7 @@
         <v>415537350482440.06</v>
       </c>
     </row>
-    <row r="12" spans="1:53">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>762</v>
       </c>
@@ -22016,7 +22010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>763</v>
       </c>
@@ -22229,7 +22223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>764</v>
       </c>
@@ -22442,7 +22436,7 @@
         <v>83311585041573.438</v>
       </c>
     </row>
-    <row r="15" spans="1:53">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>784</v>
       </c>
@@ -22655,7 +22649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:53">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>766</v>
       </c>
@@ -22868,7 +22862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>767</v>
       </c>
@@ -23081,7 +23075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>768</v>
       </c>
@@ -23294,7 +23288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>769</v>
       </c>
@@ -23507,7 +23501,7 @@
         <v>74921807049628.219</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>770</v>
       </c>
@@ -23720,7 +23714,7 @@
         <v>169704506727461.31</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>771</v>
       </c>
@@ -23933,7 +23927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>772</v>
       </c>
@@ -24158,16 +24152,16 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:BA22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
     <col min="2" max="33" width="13" customWidth="1"/>
-    <col min="34" max="34" width="16.28515625" customWidth="1"/>
+    <col min="34" max="34" width="16.33203125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
-    <col min="36" max="53" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="53" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="15.95">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>782</v>
       </c>
@@ -24328,7 +24322,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="15.95">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>751</v>
       </c>
@@ -24541,7 +24535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>752</v>
       </c>
@@ -24754,220 +24748,220 @@
         <v>250523011691.0202</v>
       </c>
     </row>
-    <row r="4" spans="1:53">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>754</v>
       </c>
       <c r="B4">
         <f>'Start Year Data'!D28</f>
-        <v>1329787419360</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f>$B4*'Time Series Scaling Factors'!C55</f>
-        <v>1598842607561.73</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f>$B4*'Time Series Scaling Factors'!D55</f>
-        <v>1867215303024.9253</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>$B4*'Time Series Scaling Factors'!E55</f>
-        <v>1975125087108.9106</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <f>$B4*'Time Series Scaling Factors'!F55</f>
-        <v>2036206259262.1741</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <f>$B4*'Time Series Scaling Factors'!G55</f>
-        <v>2188489935631.4612</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <f>$B4*'Time Series Scaling Factors'!H55</f>
-        <v>2470464435529.1294</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <f>$B4*'Time Series Scaling Factors'!I55</f>
-        <v>2729433502229.8286</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <f>$B4*'Time Series Scaling Factors'!J55</f>
-        <v>2835970885661.4023</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <f>$B4*'Time Series Scaling Factors'!K55</f>
-        <v>2942729834532.2139</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f>$B4*'Time Series Scaling Factors'!L55</f>
-        <v>3013278405955.9194</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <f>$B4*'Time Series Scaling Factors'!M55</f>
-        <v>3087428676347.0425</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <f>$B4*'Time Series Scaling Factors'!N55</f>
-        <v>3156842725943.3271</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <f>$B4*'Time Series Scaling Factors'!O55</f>
-        <v>3233894109535.4966</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f>$B4*'Time Series Scaling Factors'!P55</f>
-        <v>3271885018885.8716</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <f>$B4*'Time Series Scaling Factors'!Q55</f>
-        <v>3310982569004.3789</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <f>$B4*'Time Series Scaling Factors'!R55</f>
-        <v>3377412752042.7944</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f>$B4*'Time Series Scaling Factors'!S55</f>
-        <v>3420677927310.8667</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <f>$B4*'Time Series Scaling Factors'!T55</f>
-        <v>3420534369516.2334</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <f>$B4*'Time Series Scaling Factors'!U55</f>
-        <v>3427457770430.1309</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <f>$B4*'Time Series Scaling Factors'!V55</f>
-        <v>3434081598260.1851</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <f>$B4*'Time Series Scaling Factors'!W55</f>
-        <v>3476790635377.562</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <f>$B4*'Time Series Scaling Factors'!X55</f>
-        <v>3503696747411.7622</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <f>$B4*'Time Series Scaling Factors'!Y55</f>
-        <v>3510577140308.6719</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <f>$B4*'Time Series Scaling Factors'!Z55</f>
-        <v>3517054740880.9702</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <f>$B4*'Time Series Scaling Factors'!AA55</f>
-        <v>3529774436056.6851</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <f>$B4*'Time Series Scaling Factors'!AB55</f>
-        <v>3529259229673.8799</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f>$B4*'Time Series Scaling Factors'!AC55</f>
-        <v>3535961065148.5396</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <f>$B4*'Time Series Scaling Factors'!AD55</f>
-        <v>3544319450794.7397</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <f>$B4*'Time Series Scaling Factors'!AE55</f>
-        <v>3562006423628.9683</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <f>$B4*'Time Series Scaling Factors'!AF55</f>
-        <v>3566784762619.7524</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <f>$B4*'Time Series Scaling Factors'!AG55</f>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <f t="shared" ref="AH4:BA4" si="2">AG4</f>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AI4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AM4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AN4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AP4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AR4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AS4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AT4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AU4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AV4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AW4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AX4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AY4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="AZ4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
+        <v>0</v>
       </c>
       <c r="BA4">
         <f t="shared" si="2"/>
-        <v>3572314407176.2505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>783</v>
       </c>
@@ -25180,7 +25174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>756</v>
       </c>
@@ -25393,7 +25387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>757</v>
       </c>
@@ -25606,7 +25600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>758</v>
       </c>
@@ -25819,7 +25813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>759</v>
       </c>
@@ -26032,7 +26026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>760</v>
       </c>
@@ -26245,7 +26239,7 @@
         <v>86389732272512.844</v>
       </c>
     </row>
-    <row r="11" spans="1:53">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>761</v>
       </c>
@@ -26458,7 +26452,7 @@
         <v>36234587604575.406</v>
       </c>
     </row>
-    <row r="12" spans="1:53">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>762</v>
       </c>
@@ -26671,7 +26665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>763</v>
       </c>
@@ -26884,7 +26878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>764</v>
       </c>
@@ -27097,7 +27091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:53">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>784</v>
       </c>
@@ -27310,7 +27304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:53">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>766</v>
       </c>
@@ -27523,7 +27517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>767</v>
       </c>
@@ -27736,7 +27730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>768</v>
       </c>
@@ -27949,7 +27943,7 @@
         <v>3292900961321300.5</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>769</v>
       </c>
@@ -28162,7 +28156,7 @@
         <v>225091747925046.19</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>770</v>
       </c>
@@ -28375,7 +28369,7 @@
         <v>1864622688586.968</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>771</v>
       </c>
@@ -28588,7 +28582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>772</v>
       </c>
@@ -28810,16 +28804,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -28831,7 +28825,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" customHeight="1">
+    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="229" t="s">
         <v>80</v>
       </c>
@@ -28850,7 +28844,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="39.950000000000003">
+    <row r="3" spans="1:12" ht="36.6" x14ac:dyDescent="0.3">
       <c r="B3" s="8" t="s">
         <v>83</v>
       </c>
@@ -28883,7 +28877,7 @@
       </c>
       <c r="L3" s="231"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>93</v>
       </c>
@@ -28919,7 +28913,7 @@
         <v>1894570</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>94</v>
       </c>
@@ -28955,7 +28949,7 @@
         <v>1084477</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>96</v>
       </c>
@@ -28991,7 +28985,7 @@
         <v>190004</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>97</v>
       </c>
@@ -29027,7 +29021,7 @@
         <v>184131</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>98</v>
       </c>
@@ -29061,7 +29055,7 @@
         <v>55616</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>100</v>
       </c>
@@ -29095,7 +29089,7 @@
         <v>62183</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>101</v>
       </c>
@@ -29131,7 +29125,7 @@
         <v>37821</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>102</v>
       </c>
@@ -29167,7 +29161,7 @@
         <v>8398</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>103</v>
       </c>
@@ -29201,7 +29195,7 @@
         <v>20113</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>104</v>
       </c>
@@ -29237,7 +29231,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>105</v>
       </c>
@@ -29273,7 +29267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>106</v>
       </c>
@@ -29309,7 +29303,7 @@
         <v>4639</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>107</v>
       </c>
@@ -29345,7 +29339,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>108</v>
       </c>
@@ -29381,7 +29375,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>109</v>
       </c>
@@ -29417,7 +29411,7 @@
         <v>328230</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>110</v>
       </c>
@@ -29453,7 +29447,7 @@
         <v>29585</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>35</v>
       </c>
@@ -29485,7 +29479,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>111</v>
       </c>
@@ -29521,7 +29515,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>112</v>
       </c>
@@ -29557,7 +29551,7 @@
         <v>28092</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>113</v>
       </c>
@@ -29593,7 +29587,7 @@
         <v>23043</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>114</v>
       </c>
@@ -29629,7 +29623,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>115</v>
       </c>
@@ -29663,7 +29657,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>116</v>
       </c>
@@ -29699,7 +29693,7 @@
         <v>86337</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>117</v>
       </c>
@@ -29735,7 +29729,7 @@
         <v>212293</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>118</v>
       </c>
@@ -29771,7 +29765,7 @@
         <v>53447</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>119</v>
       </c>
@@ -29807,7 +29801,7 @@
         <v>158846</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>120</v>
       </c>
@@ -29843,7 +29837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>121</v>
       </c>
@@ -29879,7 +29873,7 @@
         <v>291859</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>122</v>
       </c>
@@ -29915,7 +29909,7 @@
         <v>24523</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>118</v>
       </c>
@@ -29949,7 +29943,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>119</v>
       </c>
@@ -29985,7 +29979,7 @@
         <v>24483</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>123</v>
       </c>
@@ -30021,7 +30015,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>124</v>
       </c>
@@ -30057,7 +30051,7 @@
         <v>41304</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>125</v>
       </c>
@@ -30093,7 +30087,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>126</v>
       </c>
@@ -30129,7 +30123,7 @@
         <v>145638</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
         <v>127</v>
       </c>
@@ -30165,7 +30159,7 @@
         <v>128016</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="15" t="s">
         <v>128</v>
       </c>
@@ -30201,7 +30195,7 @@
         <v>7480</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
         <v>129</v>
       </c>
@@ -30237,7 +30231,7 @@
         <v>10142</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>130</v>
       </c>
@@ -30273,7 +30267,7 @@
         <v>29377</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>131</v>
       </c>
@@ -30309,7 +30303,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="15" t="s">
         <v>133</v>
       </c>
@@ -30345,7 +30339,7 @@
         <v>6822</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
         <v>134</v>
       </c>
@@ -30381,7 +30375,7 @@
         <v>20621</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>135</v>
       </c>
@@ -30417,7 +30411,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="15" t="s">
         <v>136</v>
       </c>
@@ -30453,7 +30447,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="15" t="s">
         <v>137</v>
       </c>
@@ -30489,7 +30483,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>138</v>
       </c>
@@ -30525,7 +30519,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>139</v>
       </c>
@@ -30561,7 +30555,7 @@
         <v>12021</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
         <v>140</v>
       </c>
@@ -30597,7 +30591,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>141</v>
       </c>
@@ -30633,7 +30627,7 @@
         <v>8519</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>142</v>
       </c>
@@ -30669,7 +30663,7 @@
         <v>8519</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="15" t="s">
         <v>143</v>
       </c>
@@ -30707,7 +30701,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>144</v>
       </c>
@@ -30743,7 +30737,7 @@
         <v>21697</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>145</v>
       </c>
@@ -30781,7 +30775,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>146</v>
       </c>
@@ -30831,21 +30825,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>148</v>
       </c>
@@ -30865,12 +30859,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>1</v>
       </c>
@@ -30887,7 +30881,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2</v>
       </c>
@@ -30904,7 +30898,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>3</v>
       </c>
@@ -30921,7 +30915,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>4</v>
       </c>
@@ -30938,7 +30932,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>5</v>
       </c>
@@ -30955,7 +30949,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>6</v>
       </c>
@@ -30972,7 +30966,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>7</v>
       </c>
@@ -30989,7 +30983,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>8</v>
       </c>
@@ -31006,7 +31000,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>9</v>
       </c>
@@ -31023,7 +31017,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>10</v>
       </c>
@@ -31040,7 +31034,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>11</v>
       </c>
@@ -31057,7 +31051,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>12</v>
       </c>
@@ -31074,12 +31068,12 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>149</v>
       </c>
@@ -31090,7 +31084,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -31101,7 +31095,7 @@
         <v>151.07</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -31112,7 +31106,7 @@
         <v>145.75</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -31123,7 +31117,7 @@
         <v>148.58000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>4</v>
       </c>
@@ -31134,7 +31128,7 @@
         <v>155.75</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>5</v>
       </c>
@@ -31145,7 +31139,7 @@
         <v>148.33000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -31156,7 +31150,7 @@
         <v>147.9</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>7</v>
       </c>
@@ -31167,7 +31161,7 @@
         <v>166.17</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>8</v>
       </c>
@@ -31178,7 +31172,7 @@
         <v>149.41999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>9</v>
       </c>
@@ -31189,7 +31183,7 @@
         <v>153.16</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>10</v>
       </c>
@@ -31200,7 +31194,7 @@
         <v>129.94</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>11</v>
       </c>
@@ -31211,7 +31205,7 @@
         <v>144.91999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>12</v>
       </c>
@@ -31222,12 +31216,12 @@
         <v>144.99</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <f>SUM(C4:E15)</f>
         <v>6892028</v>
@@ -31236,12 +31230,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <f>SUM(B19:B30)</f>
         <v>4827647</v>
@@ -31250,27 +31244,27 @@
         <v>159</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" s="18" t="s">
         <v>86</v>
       </c>
@@ -31281,7 +31275,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2015</v>
       </c>
@@ -31295,23 +31289,23 @@
         <v>166</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <f>B44/C44</f>
         <v>4.4373853147723213E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="19">
         <f>A36*A47</f>
         <v>214221.29902704654</v>
@@ -31328,14 +31322,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="2" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>169</v>
       </c>
@@ -31344,7 +31338,7 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>170</v>
       </c>
@@ -31358,7 +31352,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -31375,7 +31369,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>172</v>
       </c>
@@ -31384,7 +31378,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>0.09</v>
       </c>
@@ -31392,7 +31386,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>775</v>
       </c>
@@ -31400,7 +31394,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>97</v>
       </c>
@@ -31408,7 +31402,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -31416,12 +31410,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>170</v>
       </c>
@@ -31435,7 +31429,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>178</v>
       </c>
@@ -31455,7 +31449,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -31473,7 +31467,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -31482,12 +31476,12 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
         <v>262.39999999999998</v>
       </c>
@@ -31495,7 +31489,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="28">
         <v>33.57</v>
       </c>
@@ -31503,7 +31497,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>67.8</v>
       </c>
@@ -31511,7 +31505,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>23.4</v>
       </c>
@@ -31519,7 +31513,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>137.69999999999999</v>
       </c>
@@ -31527,22 +31521,22 @@
         <v>186</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="28" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>190</v>
       </c>
@@ -31550,25 +31544,25 @@
         <v>191</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E28" s="4"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
@@ -31577,7 +31571,7 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>10</v>
       </c>
@@ -31585,12 +31579,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>197</v>
       </c>
@@ -31604,13 +31598,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AI100"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="15" customHeight="1" thickBot="1">
+    <row r="1" spans="1:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="199" t="s">
         <v>198</v>
       </c>
@@ -31711,8 +31705,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="15" customHeight="1" thickTop="1"/>
-    <row r="3" spans="1:35" ht="15" customHeight="1">
+    <row r="2" spans="1:35" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="218" t="s">
         <v>199</v>
       </c>
@@ -31723,7 +31717,7 @@
       <c r="F3" s="218"/>
       <c r="G3" s="218"/>
     </row>
-    <row r="4" spans="1:35" ht="15" customHeight="1">
+    <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="218" t="s">
         <v>200</v>
       </c>
@@ -31736,7 +31730,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="15" customHeight="1">
+    <row r="5" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="218" t="s">
         <v>203</v>
       </c>
@@ -31747,7 +31741,7 @@
       <c r="F5" s="218"/>
       <c r="G5" s="218"/>
     </row>
-    <row r="6" spans="1:35" ht="15" customHeight="1">
+    <row r="6" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="218" t="s">
         <v>205</v>
       </c>
@@ -31758,7 +31752,7 @@
       <c r="F6" s="218"/>
       <c r="G6" s="218"/>
     </row>
-    <row r="10" spans="1:35" ht="15" customHeight="1">
+    <row r="10" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="203" t="s">
         <v>207</v>
       </c>
@@ -31766,12 +31760,12 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="15" customHeight="1">
+    <row r="11" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="199" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="15" customHeight="1">
+    <row r="12" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="199" t="s">
         <v>210</v>
       </c>
@@ -31875,7 +31869,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="15" customHeight="1" thickBot="1">
+    <row r="13" spans="1:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="200" t="s">
         <v>212</v>
       </c>
@@ -31979,13 +31973,13 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="15" customHeight="1" thickTop="1"/>
-    <row r="15" spans="1:35" ht="15" customHeight="1">
+    <row r="14" spans="1:35" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="207" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="15" customHeight="1">
+    <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="203" t="s">
         <v>213</v>
       </c>
@@ -32092,7 +32086,7 @@
         <v>1.4128E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="15" customHeight="1">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="203" t="s">
         <v>215</v>
       </c>
@@ -32199,7 +32193,7 @@
         <v>1.5247999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="15" customHeight="1">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="203" t="s">
         <v>217</v>
       </c>
@@ -32306,7 +32300,7 @@
         <v>1.4831E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="15" customHeight="1">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="203" t="s">
         <v>219</v>
       </c>
@@ -32413,7 +32407,7 @@
         <v>-1.5231E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="15" customHeight="1">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="203" t="s">
         <v>221</v>
       </c>
@@ -32520,7 +32514,7 @@
         <v>-2.4340000000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="203" t="s">
         <v>223</v>
       </c>
@@ -32627,7 +32621,7 @@
         <v>-6.6909999999999999E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="203" t="s">
         <v>225</v>
       </c>
@@ -32734,7 +32728,7 @@
         <v>4.8079999999999998E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="15" customHeight="1">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="203" t="s">
         <v>227</v>
       </c>
@@ -32841,7 +32835,7 @@
         <v>2.9756999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="15" customHeight="1">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="203" t="s">
         <v>229</v>
       </c>
@@ -32948,7 +32942,7 @@
         <v>-2.6721000000000002E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="15" customHeight="1">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="203" t="s">
         <v>231</v>
       </c>
@@ -33055,12 +33049,12 @@
         <v>9.3290000000000005E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="15" customHeight="1">
+    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="207" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="15" customHeight="1">
+    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="203" t="s">
         <v>233</v>
       </c>
@@ -33167,7 +33161,7 @@
         <v>-3.0962E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="15" customHeight="1">
+    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="203" t="s">
         <v>235</v>
       </c>
@@ -33274,7 +33268,7 @@
         <v>-8.5459999999999998E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="15" customHeight="1">
+    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="203" t="s">
         <v>237</v>
       </c>
@@ -33381,7 +33375,7 @@
         <v>-2.9413000000000002E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="15" customHeight="1">
+    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="203" t="s">
         <v>239</v>
       </c>
@@ -33488,7 +33482,7 @@
         <v>-1.3480000000000001E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="15" customHeight="1">
+    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="203" t="s">
         <v>241</v>
       </c>
@@ -33595,12 +33589,12 @@
         <v>-2.4541E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="15" customHeight="1">
+    <row r="34" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="207" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="15" customHeight="1">
+    <row r="35" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="203" t="s">
         <v>242</v>
       </c>
@@ -33707,7 +33701,7 @@
         <v>1.1127E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="15" customHeight="1">
+    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="203" t="s">
         <v>244</v>
       </c>
@@ -33814,7 +33808,7 @@
         <v>3.2391000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="15" customHeight="1">
+    <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="203" t="s">
         <v>245</v>
       </c>
@@ -33921,7 +33915,7 @@
         <v>4.0759999999999998E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="15" customHeight="1">
+    <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="203" t="s">
         <v>247</v>
       </c>
@@ -34028,7 +34022,7 @@
         <v>1.5772000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="15" customHeight="1">
+    <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="203" t="s">
         <v>248</v>
       </c>
@@ -34135,12 +34129,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="15" customHeight="1">
+    <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="207" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="15" customHeight="1">
+    <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="203" t="s">
         <v>252</v>
       </c>
@@ -34247,7 +34241,7 @@
         <v>1.065E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="15" customHeight="1">
+    <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="203" t="s">
         <v>254</v>
       </c>
@@ -34354,7 +34348,7 @@
         <v>1.0723E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="15" customHeight="1">
+    <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="203" t="s">
         <v>255</v>
       </c>
@@ -34461,7 +34455,7 @@
         <v>-2.1780000000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="15" customHeight="1">
+    <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="203" t="s">
         <v>257</v>
       </c>
@@ -34568,7 +34562,7 @@
         <v>-2.4340000000000001E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="15" customHeight="1">
+    <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="203" t="s">
         <v>258</v>
       </c>
@@ -34675,7 +34669,7 @@
         <v>-6.6909999999999999E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="15" customHeight="1">
+    <row r="48" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="203" t="s">
         <v>259</v>
       </c>
@@ -34782,7 +34776,7 @@
         <v>4.065E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="15" customHeight="1">
+    <row r="49" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="203" t="s">
         <v>261</v>
       </c>
@@ -34889,7 +34883,7 @@
         <v>2.9756999999999999E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="15" customHeight="1">
+    <row r="50" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="203" t="s">
         <v>262</v>
       </c>
@@ -34996,7 +34990,7 @@
         <v>1.652E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="15" customHeight="1">
+    <row r="51" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="203" t="s">
         <v>264</v>
       </c>
@@ -35103,12 +35097,12 @@
         <v>2.977E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="15" customHeight="1">
+    <row r="53" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="207" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="15" customHeight="1">
+    <row r="54" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="203" t="s">
         <v>267</v>
       </c>
@@ -35215,7 +35209,7 @@
         <v>1.1879000000000001E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="15" customHeight="1">
+    <row r="55" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="203" t="s">
         <v>269</v>
       </c>
@@ -35322,7 +35316,7 @@
         <v>1.3174E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="15" customHeight="1">
+    <row r="56" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="203" t="s">
         <v>271</v>
       </c>
@@ -35429,7 +35423,7 @@
         <v>-3.7500000000000001E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="15" customHeight="1">
+    <row r="57" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="203" t="s">
         <v>273</v>
       </c>
@@ -35536,7 +35530,7 @@
         <v>4.6449999999999998E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="15" customHeight="1">
+    <row r="58" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="203" t="s">
         <v>275</v>
       </c>
@@ -35643,7 +35637,7 @@
         <v>2.2829999999999999E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="15" customHeight="1">
+    <row r="59" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="203" t="s">
         <v>277</v>
       </c>
@@ -35750,7 +35744,7 @@
         <v>-2.1199999999999999E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="15" customHeight="1">
+    <row r="60" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="203" t="s">
         <v>279</v>
       </c>
@@ -35857,12 +35851,12 @@
         <v>-3.2429999999999998E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="15" customHeight="1">
+    <row r="63" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="207" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="15" customHeight="1">
+    <row r="64" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="203" t="s">
         <v>282</v>
       </c>
@@ -35969,7 +35963,7 @@
         <v>3.6436999999999997E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="15" customHeight="1">
+    <row r="65" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="203" t="s">
         <v>283</v>
       </c>
@@ -36076,7 +36070,7 @@
         <v>3.7762999999999998E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="15" customHeight="1">
+    <row r="66" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="203" t="s">
         <v>284</v>
       </c>
@@ -36183,7 +36177,7 @@
         <v>2.3886000000000001E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="15" customHeight="1">
+    <row r="67" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="203" t="s">
         <v>285</v>
       </c>
@@ -36290,7 +36284,7 @@
         <v>2.9027000000000001E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="15" customHeight="1">
+    <row r="68" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="203" t="s">
         <v>286</v>
       </c>
@@ -36397,7 +36391,7 @@
         <v>2.6608E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="15" customHeight="1">
+    <row r="69" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="203" t="s">
         <v>287</v>
       </c>
@@ -36504,7 +36498,7 @@
         <v>2.2098E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="15" customHeight="1">
+    <row r="70" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="203" t="s">
         <v>288</v>
       </c>
@@ -36611,8 +36605,8 @@
         <v>2.0948000000000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="15" customHeight="1" thickBot="1"/>
-    <row r="72" spans="1:35" ht="15" customHeight="1">
+    <row r="71" spans="1:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="232" t="s">
         <v>289</v>
       </c>
@@ -36650,142 +36644,142 @@
       <c r="AH72" s="232"/>
       <c r="AI72" s="232"/>
     </row>
-    <row r="73" spans="1:35" ht="15" customHeight="1">
+    <row r="73" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="216" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="15" customHeight="1">
+    <row r="74" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="216" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="15" customHeight="1">
+    <row r="75" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="216" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="15" customHeight="1">
+    <row r="76" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="216" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="15" customHeight="1">
+    <row r="77" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="216" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="15" customHeight="1">
+    <row r="78" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="216" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="15" customHeight="1">
+    <row r="79" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="216" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="15" customHeight="1">
+    <row r="80" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="216" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="81" spans="2:2" ht="15" customHeight="1">
+    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="216" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="82" spans="2:2" ht="15" customHeight="1">
+    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="216" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="83" spans="2:2" ht="15" customHeight="1">
+    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="216" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="2:2" ht="15" customHeight="1">
+    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="216" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="85" spans="2:2" ht="15" customHeight="1">
+    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="216" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:2" ht="15" customHeight="1">
+    <row r="86" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="216" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="87" spans="2:2" ht="15" customHeight="1">
+    <row r="87" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="216" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="88" spans="2:2" ht="15" customHeight="1">
+    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="216" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="89" spans="2:2" ht="15" customHeight="1">
+    <row r="89" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="216" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="90" spans="2:2" ht="15" customHeight="1">
+    <row r="90" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="216" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="91" spans="2:2" ht="15" customHeight="1">
+    <row r="91" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="216" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="92" spans="2:2" ht="15" customHeight="1">
+    <row r="92" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="216" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="93" spans="2:2" ht="15" customHeight="1">
+    <row r="93" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="216" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="94" spans="2:2" ht="15" customHeight="1">
+    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="216" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="95" spans="2:2" ht="15" customHeight="1">
+    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="216" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="96" spans="2:2" ht="15" customHeight="1">
+    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="216" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="97" spans="2:2" ht="15" customHeight="1">
+    <row r="97" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="216" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="98" spans="2:2" ht="15" customHeight="1">
+    <row r="98" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="216" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="99" spans="2:2" ht="15" customHeight="1">
+    <row r="99" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="216" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="2:2" ht="15" customHeight="1">
+    <row r="100" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="216" t="s">
         <v>317</v>
       </c>
@@ -36802,13 +36796,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AH2540"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1" thickBot="1">
+    <row r="1" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="199" t="s">
         <v>318</v>
       </c>
@@ -36906,8 +36900,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15" customHeight="1" thickTop="1"/>
-    <row r="3" spans="1:34" ht="15" customHeight="1">
+    <row r="2" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="201" t="s">
         <v>199</v>
       </c>
@@ -36919,7 +36913,7 @@
       <c r="G3" s="202"/>
       <c r="H3" s="202"/>
     </row>
-    <row r="4" spans="1:34" ht="15" customHeight="1">
+    <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="201" t="s">
         <v>200</v>
       </c>
@@ -36933,7 +36927,7 @@
       </c>
       <c r="H4" s="202"/>
     </row>
-    <row r="5" spans="1:34" ht="15" customHeight="1">
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="201" t="s">
         <v>203</v>
       </c>
@@ -36945,7 +36939,7 @@
       <c r="G5" s="202"/>
       <c r="H5" s="202"/>
     </row>
-    <row r="6" spans="1:34" ht="15" customHeight="1">
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="201" t="s">
         <v>205</v>
       </c>
@@ -36957,7 +36951,7 @@
       <c r="G6" s="202"/>
       <c r="H6" s="202"/>
     </row>
-    <row r="10" spans="1:34" ht="15" customHeight="1">
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="203" t="s">
         <v>324</v>
       </c>
@@ -36968,7 +36962,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15" customHeight="1">
+    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="199" t="s">
         <v>327</v>
       </c>
@@ -36976,7 +36970,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15" customHeight="1">
+    <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="199"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -37013,7 +37007,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15" customHeight="1" thickBot="1">
+    <row r="13" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="200"/>
       <c r="C13" s="200">
         <v>2020</v>
@@ -37112,17 +37106,17 @@
         <v>330</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15" customHeight="1" thickTop="1">
+    <row r="14" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B14" s="207" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="15" customHeight="1">
+    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="207" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15" customHeight="1">
+    <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="203" t="s">
         <v>333</v>
       </c>
@@ -37226,7 +37220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="15" customHeight="1">
+    <row r="17" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="203" t="s">
         <v>335</v>
       </c>
@@ -37330,7 +37324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="15" customHeight="1">
+    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="203" t="s">
         <v>337</v>
       </c>
@@ -37434,7 +37428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="15" customHeight="1">
+    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="203" t="s">
         <v>339</v>
       </c>
@@ -37538,7 +37532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="15" customHeight="1">
+    <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="203" t="s">
         <v>341</v>
       </c>
@@ -37642,7 +37636,7 @@
         <v>-2.4000000000000001E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="15" customHeight="1">
+    <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="203" t="s">
         <v>343</v>
       </c>
@@ -37746,7 +37740,7 @@
         <v>-2.4000000000000001E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="15" customHeight="1">
+    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="203" t="s">
         <v>345</v>
       </c>
@@ -37850,7 +37844,7 @@
         <v>-2.4000000000000001E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="15" customHeight="1">
+    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="203" t="s">
         <v>347</v>
       </c>
@@ -37954,7 +37948,7 @@
         <v>-2.4000000000000001E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="15" customHeight="1">
+    <row r="24" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="203" t="s">
         <v>349</v>
       </c>
@@ -38058,7 +38052,7 @@
         <v>-2.4000000000000001E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="15" customHeight="1">
+    <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="203" t="s">
         <v>351</v>
       </c>
@@ -38162,7 +38156,7 @@
         <v>-2.4000000000000001E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="15" customHeight="1">
+    <row r="26" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="203" t="s">
         <v>353</v>
       </c>
@@ -38266,7 +38260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="15" customHeight="1">
+    <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="203" t="s">
         <v>355</v>
       </c>
@@ -38370,7 +38364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="15" customHeight="1">
+    <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="203" t="s">
         <v>357</v>
       </c>
@@ -38474,7 +38468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="15" customHeight="1">
+    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="203" t="s">
         <v>359</v>
       </c>
@@ -38578,7 +38572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="15" customHeight="1">
+    <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="203" t="s">
         <v>361</v>
       </c>
@@ -38682,7 +38676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="15" customHeight="1">
+    <row r="31" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="203" t="s">
         <v>363</v>
       </c>
@@ -38786,7 +38780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="15" customHeight="1">
+    <row r="32" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="203" t="s">
         <v>365</v>
       </c>
@@ -38890,7 +38884,7 @@
         <v>-1.6100000000000001E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="15" customHeight="1">
+    <row r="33" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="203" t="s">
         <v>367</v>
       </c>
@@ -38994,7 +38988,7 @@
         <v>-1.7799999999999999E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="15" customHeight="1">
+    <row r="34" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="203" t="s">
         <v>369</v>
       </c>
@@ -39098,7 +39092,7 @@
         <v>-1.8200000000000001E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="15.95">
+    <row r="35" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="203" t="s">
         <v>371</v>
       </c>
@@ -39202,7 +39196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="15.95">
+    <row r="36" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="203" t="s">
         <v>373</v>
       </c>
@@ -39306,7 +39300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="15.95">
+    <row r="37" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="203" t="s">
         <v>375</v>
       </c>
@@ -39410,7 +39404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="15.95">
+    <row r="38" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="203" t="s">
         <v>377</v>
       </c>
@@ -39514,7 +39508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="15.95">
+    <row r="39" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="203" t="s">
         <v>379</v>
       </c>
@@ -39618,7 +39612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="15.95">
+    <row r="40" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="203" t="s">
         <v>381</v>
       </c>
@@ -39722,7 +39716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="15.95">
+    <row r="41" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="203" t="s">
         <v>383</v>
       </c>
@@ -39826,7 +39820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="15.95">
+    <row r="42" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="203" t="s">
         <v>385</v>
       </c>
@@ -39930,7 +39924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="15.95">
+    <row r="43" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="203" t="s">
         <v>387</v>
       </c>
@@ -40034,7 +40028,7 @@
         <v>-3.4999999999999997E-5</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="15.95">
+    <row r="44" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="203" t="s">
         <v>389</v>
       </c>
@@ -40138,7 +40132,7 @@
         <v>-8.7000000000000001E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="15.95">
+    <row r="45" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="203" t="s">
         <v>391</v>
       </c>
@@ -40242,7 +40236,7 @@
         <v>-2.7E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="15.95">
+    <row r="46" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="203" t="s">
         <v>393</v>
       </c>
@@ -40346,12 +40340,12 @@
         <v>8.4099999999999995E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:34">
+    <row r="47" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B47" s="207" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="15.95">
+    <row r="48" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="203" t="s">
         <v>396</v>
       </c>
@@ -40455,7 +40449,7 @@
         <v>-1.84E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="15.95">
+    <row r="49" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="203" t="s">
         <v>398</v>
       </c>
@@ -40559,7 +40553,7 @@
         <v>1.74E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:34" ht="15" customHeight="1">
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="203" t="s">
         <v>400</v>
       </c>
@@ -40663,7 +40657,7 @@
         <v>3.6999999999999998E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:34" ht="15" customHeight="1">
+    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="203" t="s">
         <v>402</v>
       </c>
@@ -40767,12 +40761,12 @@
         <v>-5.8900000000000001E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:34" ht="15" customHeight="1">
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="207" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="203" t="s">
         <v>405</v>
       </c>
@@ -40876,7 +40870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:34" ht="15" customHeight="1">
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="203" t="s">
         <v>407</v>
       </c>
@@ -40980,7 +40974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:34" ht="15" customHeight="1">
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="203" t="s">
         <v>409</v>
       </c>
@@ -41084,7 +41078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:34" ht="15" customHeight="1">
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="203" t="s">
         <v>411</v>
       </c>
@@ -41188,7 +41182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:34" ht="15" customHeight="1">
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="203" t="s">
         <v>413</v>
       </c>
@@ -41292,7 +41286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:34" ht="15" customHeight="1">
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="203" t="s">
         <v>415</v>
       </c>
@@ -41396,7 +41390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:34" ht="15" customHeight="1">
+    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="203" t="s">
         <v>417</v>
       </c>
@@ -41500,12 +41494,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:34">
+    <row r="62" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B62" s="207" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="63" spans="1:34" ht="15" customHeight="1">
+    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="203" t="s">
         <v>420</v>
       </c>
@@ -41609,7 +41603,7 @@
         <v>8.4099999999999995E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:34" ht="15" customHeight="1">
+    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="203" t="s">
         <v>421</v>
       </c>
@@ -41713,7 +41707,7 @@
         <v>-1.9100000000000001E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:34" ht="15" customHeight="1">
+    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="203" t="s">
         <v>423</v>
       </c>
@@ -41817,7 +41811,7 @@
         <v>-6.2600000000000004E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:34" ht="15" customHeight="1">
+    <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="203" t="s">
         <v>425</v>
       </c>
@@ -41921,7 +41915,7 @@
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:34" ht="15" customHeight="1">
+    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="203" t="s">
         <v>426</v>
       </c>
@@ -42025,7 +42019,7 @@
         <v>-1.126E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:34" ht="15" customHeight="1">
+    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="203" t="s">
         <v>428</v>
       </c>
@@ -42129,7 +42123,7 @@
         <v>4.73E-4</v>
       </c>
     </row>
-    <row r="69" spans="1:34" ht="15" customHeight="1">
+    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="203" t="s">
         <v>430</v>
       </c>
@@ -42233,7 +42227,7 @@
         <v>-5.5999999999999999E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:34" ht="15.95">
+    <row r="70" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="203" t="s">
         <v>432</v>
       </c>
@@ -42337,7 +42331,7 @@
         <v>1.3999999999999999E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:34" ht="15" customHeight="1">
+    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="203" t="s">
         <v>434</v>
       </c>
@@ -42441,7 +42435,7 @@
         <v>3.581E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:34" ht="15" customHeight="1">
+    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="203" t="s">
         <v>435</v>
       </c>
@@ -42545,7 +42539,7 @@
         <v>-1.4339999999999999E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:34" ht="15" customHeight="1">
+    <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="203" t="s">
         <v>436</v>
       </c>
@@ -42649,7 +42643,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:34" ht="15" customHeight="1">
+    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="203" t="s">
         <v>438</v>
       </c>
@@ -42753,17 +42747,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:34" ht="15" customHeight="1">
+    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="207" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="77" spans="1:34" ht="15" customHeight="1">
+    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="207" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="78" spans="1:34" ht="15.95">
+    <row r="78" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="203" t="s">
         <v>442</v>
       </c>
@@ -42867,7 +42861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:34" ht="15" customHeight="1" thickBot="1">
+    <row r="79" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="203" t="s">
         <v>444</v>
       </c>
@@ -42971,7 +42965,7 @@
         <v>-4.2760000000000003E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:34" ht="15" customHeight="1">
+    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="233" t="s">
         <v>446</v>
       </c>
@@ -43008,32 +43002,32 @@
       <c r="AG80" s="234"/>
       <c r="AH80" s="215"/>
     </row>
-    <row r="81" spans="2:34" ht="15" customHeight="1">
+    <row r="81" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="216" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="82" spans="2:34" ht="15" customHeight="1">
+    <row r="82" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="216" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="83" spans="2:34" ht="15" customHeight="1">
+    <row r="83" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="216" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="84" spans="2:34">
+    <row r="84" spans="2:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B84" s="216" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="85" spans="2:34" ht="15" customHeight="1">
+    <row r="85" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="216" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="88" spans="2:34" ht="15" customHeight="1">
+    <row r="88" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="235"/>
       <c r="C88" s="235"/>
       <c r="D88" s="235"/>
@@ -43068,7 +43062,7 @@
       <c r="AG88" s="235"/>
       <c r="AH88" s="235"/>
     </row>
-    <row r="213" spans="2:34" ht="15" customHeight="1">
+    <row r="213" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B213" s="235"/>
       <c r="C213" s="235"/>
       <c r="D213" s="235"/>
@@ -43103,7 +43097,7 @@
       <c r="AG213" s="235"/>
       <c r="AH213" s="235"/>
     </row>
-    <row r="379" spans="2:34" ht="15" customHeight="1">
+    <row r="379" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B379" s="235"/>
       <c r="C379" s="235"/>
       <c r="D379" s="235"/>
@@ -43138,7 +43132,7 @@
       <c r="AG379" s="235"/>
       <c r="AH379" s="235"/>
     </row>
-    <row r="496" spans="2:34" ht="15" customHeight="1">
+    <row r="496" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B496" s="235"/>
       <c r="C496" s="235"/>
       <c r="D496" s="235"/>
@@ -43173,7 +43167,7 @@
       <c r="AG496" s="235"/>
       <c r="AH496" s="235"/>
     </row>
-    <row r="648" spans="2:34" ht="15" customHeight="1">
+    <row r="648" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B648" s="235"/>
       <c r="C648" s="235"/>
       <c r="D648" s="235"/>
@@ -43208,7 +43202,7 @@
       <c r="AG648" s="235"/>
       <c r="AH648" s="235"/>
     </row>
-    <row r="748" spans="2:34" ht="15" customHeight="1">
+    <row r="748" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B748" s="235"/>
       <c r="C748" s="235"/>
       <c r="D748" s="235"/>
@@ -43243,7 +43237,7 @@
       <c r="AG748" s="235"/>
       <c r="AH748" s="235"/>
     </row>
-    <row r="839" spans="2:34" ht="15" customHeight="1">
+    <row r="839" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B839" s="235"/>
       <c r="C839" s="235"/>
       <c r="D839" s="235"/>
@@ -43278,7 +43272,7 @@
       <c r="AG839" s="235"/>
       <c r="AH839" s="235"/>
     </row>
-    <row r="910" spans="2:34" ht="15" customHeight="1">
+    <row r="910" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B910" s="235"/>
       <c r="C910" s="235"/>
       <c r="D910" s="235"/>
@@ -43313,7 +43307,7 @@
       <c r="AG910" s="235"/>
       <c r="AH910" s="235"/>
     </row>
-    <row r="1005" spans="2:34" ht="15" customHeight="1">
+    <row r="1005" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1005" s="235"/>
       <c r="C1005" s="235"/>
       <c r="D1005" s="235"/>
@@ -43348,7 +43342,7 @@
       <c r="AG1005" s="235"/>
       <c r="AH1005" s="235"/>
     </row>
-    <row r="1105" spans="2:34" ht="15" customHeight="1">
+    <row r="1105" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1105" s="235"/>
       <c r="C1105" s="235"/>
       <c r="D1105" s="235"/>
@@ -43383,7 +43377,7 @@
       <c r="AG1105" s="235"/>
       <c r="AH1105" s="235"/>
     </row>
-    <row r="1180" spans="2:34" ht="15" customHeight="1">
+    <row r="1180" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1180" s="235"/>
       <c r="C1180" s="235"/>
       <c r="D1180" s="235"/>
@@ -43418,7 +43412,7 @@
       <c r="AG1180" s="235"/>
       <c r="AH1180" s="235"/>
     </row>
-    <row r="1255" spans="2:34" ht="15" customHeight="1">
+    <row r="1255" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1255" s="235"/>
       <c r="C1255" s="235"/>
       <c r="D1255" s="235"/>
@@ -43453,7 +43447,7 @@
       <c r="AG1255" s="235"/>
       <c r="AH1255" s="235"/>
     </row>
-    <row r="1355" spans="2:34" ht="15" customHeight="1">
+    <row r="1355" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1355" s="235"/>
       <c r="C1355" s="235"/>
       <c r="D1355" s="235"/>
@@ -43488,7 +43482,7 @@
       <c r="AG1355" s="235"/>
       <c r="AH1355" s="235"/>
     </row>
-    <row r="1527" spans="2:34" ht="15" customHeight="1">
+    <row r="1527" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1527" s="235"/>
       <c r="C1527" s="235"/>
       <c r="D1527" s="235"/>
@@ -43523,7 +43517,7 @@
       <c r="AG1527" s="235"/>
       <c r="AH1527" s="235"/>
     </row>
-    <row r="1622" spans="2:34" ht="15" customHeight="1">
+    <row r="1622" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1622" s="235"/>
       <c r="C1622" s="235"/>
       <c r="D1622" s="235"/>
@@ -43558,7 +43552,7 @@
       <c r="AG1622" s="235"/>
       <c r="AH1622" s="235"/>
     </row>
-    <row r="1740" spans="2:34" ht="15" customHeight="1">
+    <row r="1740" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1740" s="235"/>
       <c r="C1740" s="235"/>
       <c r="D1740" s="235"/>
@@ -43593,7 +43587,7 @@
       <c r="AG1740" s="235"/>
       <c r="AH1740" s="235"/>
     </row>
-    <row r="1840" spans="2:34" ht="15" customHeight="1">
+    <row r="1840" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1840" s="235"/>
       <c r="C1840" s="235"/>
       <c r="D1840" s="235"/>
@@ -43628,7 +43622,7 @@
       <c r="AG1840" s="235"/>
       <c r="AH1840" s="235"/>
     </row>
-    <row r="1940" spans="2:34" ht="15" customHeight="1">
+    <row r="1940" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1940" s="235"/>
       <c r="C1940" s="235"/>
       <c r="D1940" s="235"/>
@@ -43663,7 +43657,7 @@
       <c r="AG1940" s="235"/>
       <c r="AH1940" s="235"/>
     </row>
-    <row r="2040" spans="2:34" ht="15" customHeight="1">
+    <row r="2040" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2040" s="235"/>
       <c r="C2040" s="235"/>
       <c r="D2040" s="235"/>
@@ -43698,7 +43692,7 @@
       <c r="AG2040" s="235"/>
       <c r="AH2040" s="235"/>
     </row>
-    <row r="2140" spans="2:34" ht="15" customHeight="1">
+    <row r="2140" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2140" s="235"/>
       <c r="C2140" s="235"/>
       <c r="D2140" s="235"/>
@@ -43733,7 +43727,7 @@
       <c r="AG2140" s="235"/>
       <c r="AH2140" s="235"/>
     </row>
-    <row r="2240" spans="2:34" ht="15" customHeight="1">
+    <row r="2240" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2240" s="235"/>
       <c r="C2240" s="235"/>
       <c r="D2240" s="235"/>
@@ -43768,7 +43762,7 @@
       <c r="AG2240" s="235"/>
       <c r="AH2240" s="235"/>
     </row>
-    <row r="2340" spans="2:34" ht="15" customHeight="1">
+    <row r="2340" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2340" s="235"/>
       <c r="C2340" s="235"/>
       <c r="D2340" s="235"/>
@@ -43803,7 +43797,7 @@
       <c r="AG2340" s="235"/>
       <c r="AH2340" s="235"/>
     </row>
-    <row r="2440" spans="2:34" ht="15" customHeight="1">
+    <row r="2440" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2440" s="235"/>
       <c r="C2440" s="235"/>
       <c r="D2440" s="235"/>
@@ -43838,7 +43832,7 @@
       <c r="AG2440" s="235"/>
       <c r="AH2440" s="235"/>
     </row>
-    <row r="2540" spans="2:34" ht="15" customHeight="1">
+    <row r="2540" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2540" s="235"/>
       <c r="C2540" s="235"/>
       <c r="D2540" s="235"/>
@@ -43875,21 +43869,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B80:AG80"/>
-    <mergeCell ref="B88:AH88"/>
-    <mergeCell ref="B213:AH213"/>
-    <mergeCell ref="B379:AH379"/>
-    <mergeCell ref="B496:AH496"/>
-    <mergeCell ref="B648:AH648"/>
-    <mergeCell ref="B748:AH748"/>
-    <mergeCell ref="B839:AH839"/>
-    <mergeCell ref="B910:AH910"/>
-    <mergeCell ref="B1005:AH1005"/>
-    <mergeCell ref="B1105:AH1105"/>
-    <mergeCell ref="B1180:AH1180"/>
-    <mergeCell ref="B1255:AH1255"/>
-    <mergeCell ref="B1355:AH1355"/>
-    <mergeCell ref="B1527:AH1527"/>
     <mergeCell ref="B1622:AH1622"/>
     <mergeCell ref="B1740:AH1740"/>
     <mergeCell ref="B1840:AH1840"/>
@@ -43900,6 +43879,21 @@
     <mergeCell ref="B2240:AH2240"/>
     <mergeCell ref="B2340:AH2340"/>
     <mergeCell ref="B2440:AH2440"/>
+    <mergeCell ref="B1105:AH1105"/>
+    <mergeCell ref="B1180:AH1180"/>
+    <mergeCell ref="B1255:AH1255"/>
+    <mergeCell ref="B1355:AH1355"/>
+    <mergeCell ref="B1527:AH1527"/>
+    <mergeCell ref="B648:AH648"/>
+    <mergeCell ref="B748:AH748"/>
+    <mergeCell ref="B839:AH839"/>
+    <mergeCell ref="B910:AH910"/>
+    <mergeCell ref="B1005:AH1005"/>
+    <mergeCell ref="B80:AG80"/>
+    <mergeCell ref="B88:AH88"/>
+    <mergeCell ref="B213:AH213"/>
+    <mergeCell ref="B379:AH379"/>
+    <mergeCell ref="B496:AH496"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43909,35 +43903,35 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:X163"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.42578125" customWidth="1"/>
-    <col min="23" max="23" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.44140625" customWidth="1"/>
+    <col min="23" max="23" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.95">
+    <row r="1" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="36" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="12.75" customHeight="1">
+    <row r="3" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38" t="s">
         <v>454</v>
       </c>
@@ -43960,7 +43954,7 @@
       </c>
       <c r="I3" s="42"/>
     </row>
-    <row r="4" spans="1:23" ht="29.1">
+    <row r="4" spans="1:23" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="43"/>
       <c r="B4" s="44" t="s">
         <v>459</v>
@@ -43985,7 +43979,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="48" t="s">
         <v>466</v>
       </c>
@@ -44002,7 +43996,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>468</v>
       </c>
@@ -44023,7 +44017,7 @@
       <c r="H6" s="56"/>
       <c r="I6" s="57"/>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>471</v>
       </c>
@@ -44052,7 +44046,7 @@
         <v>0.93726057101554028</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>472</v>
       </c>
@@ -44081,7 +44075,7 @@
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>473</v>
       </c>
@@ -44110,7 +44104,7 @@
         <v>0.93500000000000016</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="58" t="s">
         <v>474</v>
       </c>
@@ -44139,7 +44133,7 @@
         <v>0.93500000000000016</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>475</v>
       </c>
@@ -44176,7 +44170,7 @@
       <c r="R11" s="63"/>
       <c r="S11" s="69"/>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>476</v>
       </c>
@@ -44205,7 +44199,7 @@
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>477</v>
       </c>
@@ -44234,7 +44228,7 @@
         <v>0.93726057101554028</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>478</v>
       </c>
@@ -44263,7 +44257,7 @@
         <v>0.93726057101554017</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>479</v>
       </c>
@@ -44300,7 +44294,7 @@
       <c r="V15" s="28"/>
       <c r="W15" s="70"/>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
         <v>480</v>
       </c>
@@ -44334,7 +44328,7 @@
       <c r="V16" s="28"/>
       <c r="W16" s="70"/>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>481</v>
       </c>
@@ -44371,7 +44365,7 @@
       <c r="V17" s="28"/>
       <c r="W17" s="70"/>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="58" t="s">
         <v>482</v>
       </c>
@@ -44405,7 +44399,7 @@
       <c r="V18" s="28"/>
       <c r="W18" s="70"/>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>483</v>
       </c>
@@ -44439,7 +44433,7 @@
       <c r="M19" s="28"/>
       <c r="N19" s="70"/>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="58" t="s">
         <v>484</v>
       </c>
@@ -44469,7 +44463,7 @@
       </c>
       <c r="W20" s="70"/>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="75" t="s">
         <v>485</v>
       </c>
@@ -44496,7 +44490,7 @@
       </c>
       <c r="I21" s="64"/>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="58" t="s">
         <v>486</v>
       </c>
@@ -44525,7 +44519,7 @@
         <v>0.93499781627602274</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>487</v>
       </c>
@@ -44554,7 +44548,7 @@
         <v>0.93499781627602274</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>488</v>
       </c>
@@ -44583,7 +44577,7 @@
         <v>0.93476175247841387</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>489</v>
       </c>
@@ -44612,7 +44606,7 @@
         <v>0.93404711473172097</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="58" t="s">
         <v>490</v>
       </c>
@@ -44641,7 +44635,7 @@
         <v>0.93500003751584637</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>491</v>
       </c>
@@ -44670,7 +44664,7 @@
         <v>0.93500003751584626</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="58" t="s">
         <v>492</v>
       </c>
@@ -44699,7 +44693,7 @@
         <v>0.93135126106564226</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="58" t="s">
         <v>493</v>
       </c>
@@ -44728,7 +44722,7 @@
         <v>0.93499781627602263</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="58" t="s">
         <v>494</v>
       </c>
@@ -44757,7 +44751,7 @@
         <v>0.93499781627602263</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="58" t="s">
         <v>495</v>
       </c>
@@ -44786,7 +44780,7 @@
         <v>0.87806748466257667</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="58" t="s">
         <v>496</v>
       </c>
@@ -44815,7 +44809,7 @@
         <v>0.90299302022950434</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="58" t="s">
         <v>497</v>
       </c>
@@ -44844,7 +44838,7 @@
         <v>0.92051300964428628</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="58" t="s">
         <v>498</v>
       </c>
@@ -44873,7 +44867,7 @@
         <v>0.92867915675168411</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="58" t="s">
         <v>499</v>
       </c>
@@ -44902,7 +44896,7 @@
         <v>0.93364967025896739</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="58" t="s">
         <v>500</v>
       </c>
@@ -44931,7 +44925,7 @@
         <v>0.9293293950333662</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="58" t="s">
         <v>501</v>
       </c>
@@ -44960,7 +44954,7 @@
         <v>0.88092431030417351</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="58" t="s">
         <v>502</v>
       </c>
@@ -44989,7 +44983,7 @@
         <v>0.91165189789710355</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="58" t="s">
         <v>503</v>
       </c>
@@ -45018,7 +45012,7 @@
         <v>0.91165189789710355</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="58" t="s">
         <v>504</v>
       </c>
@@ -45047,7 +45041,7 @@
         <v>0.93427633635511098</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="58" t="s">
         <v>505</v>
       </c>
@@ -45076,7 +45070,7 @@
         <v>0.95108821041298164</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="58" t="s">
         <v>506</v>
       </c>
@@ -45105,7 +45099,7 @@
         <v>0.93427633635511098</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="58" t="s">
         <v>507</v>
       </c>
@@ -45134,7 +45128,7 @@
         <v>0.93938096730547249</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="58" t="s">
         <v>508</v>
       </c>
@@ -45163,7 +45157,7 @@
         <v>0.92840083590406852</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>509</v>
       </c>
@@ -45192,7 +45186,7 @@
         <v>0.93361506882395562</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="58" t="s">
         <v>510</v>
       </c>
@@ -45221,7 +45215,7 @@
         <v>0.93361506882395551</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="58" t="s">
         <v>511</v>
       </c>
@@ -45250,7 +45244,7 @@
         <v>0.93361506882395551</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="58" t="s">
         <v>512</v>
       </c>
@@ -45279,7 +45273,7 @@
         <v>0.93500003751584626</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="58" t="s">
         <v>513</v>
       </c>
@@ -45308,7 +45302,7 @@
         <v>0.84675180455302612</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="58" t="s">
         <v>514</v>
       </c>
@@ -45337,7 +45331,7 @@
         <v>0.92494808662118067</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="58" t="s">
         <v>515</v>
       </c>
@@ -45366,7 +45360,7 @@
         <v>0.92528460728977324</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="58" t="s">
         <v>516</v>
       </c>
@@ -45395,7 +45389,7 @@
         <v>0.92548586165607438</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="58" t="s">
         <v>517</v>
       </c>
@@ -45424,7 +45418,7 @@
         <v>0.92007362914163926</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="58" t="s">
         <v>102</v>
       </c>
@@ -45453,7 +45447,7 @@
         <v>0.91375811688311692</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="58" t="s">
         <v>108</v>
       </c>
@@ -45482,7 +45476,7 @@
         <v>0.92923017182797785</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="58" t="s">
         <v>100</v>
       </c>
@@ -45511,7 +45505,7 @@
         <v>0.92157077225989936</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="58" t="s">
         <v>518</v>
       </c>
@@ -45538,7 +45532,7 @@
         <v>0.92932939503336609</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="53" t="s">
         <v>519</v>
       </c>
@@ -45567,7 +45561,7 @@
         <v>0.93722267739953979</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="58" t="s">
         <v>520</v>
       </c>
@@ -45590,7 +45584,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="58" t="s">
         <v>523</v>
       </c>
@@ -45619,7 +45613,7 @@
         <v>0.90266299357208446</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="58" t="s">
         <v>524</v>
       </c>
@@ -45648,7 +45642,7 @@
         <v>0.9009009009009008</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="58" t="s">
         <v>525</v>
       </c>
@@ -45677,7 +45671,7 @@
         <v>0.84548104956268222</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="58" t="s">
         <v>526</v>
       </c>
@@ -45698,7 +45692,7 @@
       </c>
       <c r="I63" s="64"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="53" t="s">
         <v>527</v>
       </c>
@@ -45727,7 +45721,7 @@
         <v>0.90586790472651468</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="58" t="s">
         <v>528</v>
       </c>
@@ -45748,7 +45742,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="75" t="s">
         <v>530</v>
       </c>
@@ -45774,7 +45768,7 @@
       <c r="I66" s="97"/>
       <c r="K66" s="98"/>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="75" t="s">
         <v>531</v>
       </c>
@@ -45802,7 +45796,7 @@
       </c>
       <c r="K67" s="98"/>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="75" t="s">
         <v>532</v>
       </c>
@@ -45830,7 +45824,7 @@
       </c>
       <c r="K68" s="98"/>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="75" t="s">
         <v>533</v>
       </c>
@@ -45858,7 +45852,7 @@
       </c>
       <c r="K69" s="98"/>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="75" t="s">
         <v>534</v>
       </c>
@@ -45886,7 +45880,7 @@
       </c>
       <c r="K70" s="98"/>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="58" t="s">
         <v>535</v>
       </c>
@@ -45915,7 +45909,7 @@
       <c r="K71" s="98"/>
       <c r="L71" s="98"/>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="58" t="s">
         <v>536</v>
       </c>
@@ -45943,7 +45937,7 @@
       </c>
       <c r="K72" s="98"/>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="58" t="s">
         <v>537</v>
       </c>
@@ -45970,7 +45964,7 @@
         <v>0.94242199100000001</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="12.6" customHeight="1">
+    <row r="74" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="58" t="s">
         <v>538</v>
       </c>
@@ -45998,7 +45992,7 @@
       </c>
       <c r="K74" s="100"/>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="58" t="s">
         <v>539</v>
       </c>
@@ -46026,7 +46020,7 @@
       </c>
       <c r="K75" s="100"/>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="58" t="s">
         <v>540</v>
       </c>
@@ -46053,7 +46047,7 @@
         <v>0.93173565722585328</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="58" t="s">
         <v>541</v>
       </c>
@@ -46081,7 +46075,7 @@
       </c>
       <c r="K77" s="101"/>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="58" t="s">
         <v>542</v>
       </c>
@@ -46109,7 +46103,7 @@
       </c>
       <c r="K78" s="100"/>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="58" t="s">
         <v>543</v>
       </c>
@@ -46136,7 +46130,7 @@
         <v>0.93680161201685286</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="58" t="s">
         <v>544</v>
       </c>
@@ -46163,7 +46157,7 @@
         <v>0.93292760238366934</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="58" t="s">
         <v>545</v>
       </c>
@@ -46190,7 +46184,7 @@
         <v>0.96554227633195577</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="58" t="s">
         <v>546</v>
       </c>
@@ -46217,7 +46211,7 @@
         <v>0.93359512366662756</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="75" t="s">
         <v>547</v>
       </c>
@@ -46240,7 +46234,7 @@
       </c>
       <c r="I83" s="104"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="105" t="s">
         <v>548</v>
       </c>
@@ -46263,7 +46257,7 @@
         <v>0.85292563033160751</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="105" t="s">
         <v>549</v>
       </c>
@@ -46286,7 +46280,7 @@
         <v>0.88047037071579148</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="105" t="s">
         <v>550</v>
       </c>
@@ -46313,7 +46307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="108" t="s">
         <v>551</v>
       </c>
@@ -46340,7 +46334,7 @@
         <v>0.90447216306662592</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="109" t="s">
         <v>552</v>
       </c>
@@ -46367,7 +46361,7 @@
         <v>0.94150280898876404</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>553</v>
       </c>
@@ -46394,7 +46388,7 @@
         <v>0.94150280898876404</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="37" t="s">
         <v>554</v>
       </c>
@@ -46421,7 +46415,7 @@
         <v>0.8252427184466018</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>555</v>
       </c>
@@ -46448,7 +46442,7 @@
         <v>0.87681159420289856</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="120" t="s">
         <v>556</v>
       </c>
@@ -46482,7 +46476,7 @@
       <c r="M92" s="123"/>
       <c r="N92" s="124"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="125" t="s">
         <v>139</v>
       </c>
@@ -46508,19 +46502,19 @@
       <c r="M93" s="127"/>
       <c r="N93" s="128"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="129"/>
       <c r="B94" s="130"/>
       <c r="N94" s="131"/>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="129" t="s">
         <v>557</v>
       </c>
       <c r="B95" s="130"/>
       <c r="N95" s="131"/>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="125" t="s">
         <v>558</v>
       </c>
@@ -46538,7 +46532,7 @@
       <c r="M96" s="133"/>
       <c r="N96" s="134"/>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="18" t="s">
         <v>559</v>
       </c>
@@ -46582,7 +46576,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>566</v>
       </c>
@@ -46626,7 +46620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="135" t="s">
         <v>567</v>
       </c>
@@ -46670,7 +46664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="125" t="s">
         <v>568</v>
       </c>
@@ -46714,7 +46708,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="129" t="s">
         <v>569</v>
       </c>
@@ -46758,19 +46752,19 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="129"/>
       <c r="B102" s="130"/>
       <c r="G102" s="131"/>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="129" t="s">
         <v>570</v>
       </c>
       <c r="B103" s="130"/>
       <c r="G103" s="131"/>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="129" t="s">
         <v>571</v>
       </c>
@@ -46793,7 +46787,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="125" t="s">
         <v>566</v>
       </c>
@@ -46814,7 +46808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>575</v>
       </c>
@@ -46837,7 +46831,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="37" t="s">
         <v>576</v>
       </c>
@@ -46860,7 +46854,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="120" t="s">
         <v>577</v>
       </c>
@@ -46883,7 +46877,7 @@
         <v>-87</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="129" t="s">
         <v>578</v>
       </c>
@@ -46906,7 +46900,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="129" t="s">
         <v>579</v>
       </c>
@@ -46929,17 +46923,17 @@
         <v>-71</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="129"/>
       <c r="B111" s="144"/>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="125" t="s">
         <v>580</v>
       </c>
       <c r="B112" s="145"/>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>581</v>
       </c>
@@ -46947,7 +46941,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="37" t="s">
         <v>582</v>
       </c>
@@ -46955,7 +46949,7 @@
         <v>0.42857142857142855</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>583</v>
       </c>
@@ -46963,7 +46957,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>584</v>
       </c>
@@ -46976,7 +46970,7 @@
       <c r="R116" s="148"/>
       <c r="V116" s="148"/>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>585</v>
       </c>
@@ -46989,7 +46983,7 @@
       <c r="R117" s="151"/>
       <c r="V117" s="151"/>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B118" s="152"/>
       <c r="C118" s="153"/>
       <c r="D118" s="154"/>
@@ -47009,7 +47003,7 @@
       <c r="W118" s="155"/>
       <c r="X118" s="154"/>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>586</v>
       </c>
@@ -47032,7 +47026,7 @@
       <c r="W119" s="157"/>
       <c r="X119" s="158"/>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B120" s="159"/>
       <c r="C120" s="151"/>
       <c r="D120" s="160"/>
@@ -47052,7 +47046,7 @@
       <c r="W120" s="151"/>
       <c r="X120" s="160"/>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B121" s="159">
         <v>10</v>
       </c>
@@ -47084,7 +47078,7 @@
       <c r="W121" s="151"/>
       <c r="X121" s="160"/>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B122" s="159">
         <v>10</v>
       </c>
@@ -47116,7 +47110,7 @@
       <c r="W122" s="151"/>
       <c r="X122" s="160"/>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B123" s="159" t="s">
         <v>587</v>
       </c>
@@ -47172,7 +47166,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B124" s="159">
         <v>1990</v>
       </c>
@@ -47228,7 +47222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B125" s="159">
         <v>1995</v>
       </c>
@@ -47284,7 +47278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B126" s="164">
         <v>2000</v>
       </c>
@@ -47340,7 +47334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>2005</v>
       </c>
@@ -47396,7 +47390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="37"/>
       <c r="B128">
         <v>2010</v>
@@ -47453,7 +47447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A129" s="167"/>
       <c r="B129" s="168">
         <v>2015</v>
@@ -47511,7 +47505,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130" s="170"/>
       <c r="B130" s="171">
         <v>2017</v>
@@ -47569,7 +47563,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131" s="170"/>
       <c r="B131" s="174">
         <v>2020</v>
@@ -47583,7 +47577,7 @@
       <c r="E131" s="172"/>
       <c r="F131" s="175"/>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132" s="170"/>
       <c r="B132" s="174"/>
       <c r="C132" s="174"/>
@@ -47591,7 +47585,7 @@
       <c r="E132" s="174"/>
       <c r="F132" s="175"/>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133" s="170" t="s">
         <v>595</v>
       </c>
@@ -47601,7 +47595,7 @@
       <c r="E133" s="171"/>
       <c r="F133" s="173"/>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134" s="176" t="s">
         <v>596</v>
       </c>
@@ -47621,7 +47615,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>602</v>
       </c>
@@ -47641,7 +47635,7 @@
         <v>907184.74</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136" s="167" t="s">
         <v>166</v>
       </c>
@@ -47661,7 +47655,7 @@
         <v>907.18474000000003</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137" s="170" t="s">
         <v>603</v>
       </c>
@@ -47681,7 +47675,7 @@
         <v>0.90718474000000004</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138" s="170" t="s">
         <v>604</v>
       </c>
@@ -47701,7 +47695,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139" s="170" t="s">
         <v>605</v>
       </c>
@@ -47721,7 +47715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140" s="170"/>
       <c r="B140" s="151"/>
       <c r="C140" s="174"/>
@@ -47729,7 +47723,7 @@
       <c r="E140" s="171"/>
       <c r="F140" s="175"/>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141" s="176" t="s">
         <v>606</v>
       </c>
@@ -47749,7 +47743,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>612</v>
       </c>
@@ -47769,7 +47763,7 @@
         <v>2.8316846999999999E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143" s="167" t="s">
         <v>613</v>
       </c>
@@ -47792,7 +47786,7 @@
       <c r="H143" s="168"/>
       <c r="I143" s="169"/>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144" s="170" t="s">
         <v>614</v>
       </c>
@@ -47815,7 +47809,7 @@
       <c r="H144" s="171"/>
       <c r="I144" s="131"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="170" t="s">
         <v>615</v>
       </c>
@@ -47838,7 +47832,7 @@
       <c r="H145" s="171"/>
       <c r="I145" s="131"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="170" t="s">
         <v>616</v>
       </c>
@@ -47861,7 +47855,7 @@
       <c r="H146" s="171"/>
       <c r="I146" s="131"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="170"/>
       <c r="B147" s="174"/>
       <c r="C147" s="172"/>
@@ -47872,7 +47866,7 @@
       <c r="H147" s="171"/>
       <c r="I147" s="131"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="170" t="s">
         <v>617</v>
       </c>
@@ -47901,7 +47895,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="170" t="s">
         <v>626</v>
       </c>
@@ -47930,7 +47924,7 @@
         <v>2684519.5376862194</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="170" t="s">
         <v>627</v>
       </c>
@@ -47959,7 +47953,7 @@
         <v>2684.5195376862198</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="176" t="s">
         <v>628</v>
       </c>
@@ -47988,7 +47982,7 @@
         <v>2.6845195376862194</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>629</v>
       </c>
@@ -48017,7 +48011,7 @@
         <v>745.69987157950538</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>630</v>
       </c>
@@ -48046,7 +48040,7 @@
         <v>0.74569987157950535</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>631</v>
       </c>
@@ -48075,7 +48069,7 @@
         <v>2544.4335839531336</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>632</v>
       </c>
@@ -48104,7 +48098,7 @@
         <v>2.5444335839531337E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>633</v>
       </c>
@@ -48133,7 +48127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>634</v>
       </c>
@@ -48153,7 +48147,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>635</v>
       </c>
@@ -48173,7 +48167,7 @@
         <v>1609340</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>636</v>
       </c>
@@ -48193,7 +48187,7 @@
         <v>1609.34</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>637</v>
       </c>
@@ -48213,7 +48207,7 @@
         <v>1.60934</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>638</v>
       </c>
@@ -48233,7 +48227,7 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>639</v>
       </c>
@@ -48282,43 +48276,43 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:P93"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" style="219" customWidth="1"/>
-    <col min="2" max="16384" width="10.85546875" style="219"/>
+    <col min="1" max="1" width="33.6640625" style="219" customWidth="1"/>
+    <col min="2" max="16384" width="10.88671875" style="219"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="219" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="219" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="219" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="222" customFormat="1">
+    <row r="4" spans="1:16" s="222" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="222" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="219" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B7" s="219" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="223" t="s">
         <v>646</v>
       </c>
@@ -48368,7 +48362,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="219" t="s">
         <v>647</v>
       </c>
@@ -48418,7 +48412,7 @@
         <v>8811.0535930000005</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="219" t="s">
         <v>648</v>
       </c>
@@ -48468,7 +48462,7 @@
         <v>541.49340500000005</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="219" t="s">
         <v>649</v>
       </c>
@@ -48518,7 +48512,7 @@
         <v>3261.141932</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="219" t="s">
         <v>650</v>
       </c>
@@ -48568,7 +48562,7 @@
         <v>4227.1734029999998</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="219" t="s">
         <v>651</v>
       </c>
@@ -48618,7 +48612,7 @@
         <v>124.82</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="219" t="s">
         <v>652</v>
       </c>
@@ -48668,7 +48662,7 @@
         <v>661.12485300000003</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="219" t="s">
         <v>653</v>
       </c>
@@ -48718,7 +48712,7 @@
         <v>2.7989999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="219" t="s">
         <v>654</v>
       </c>
@@ -48768,7 +48762,7 @@
         <v>84.99</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="219" t="s">
         <v>655</v>
       </c>
@@ -48818,7 +48812,7 @@
         <v>213.42</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="219" t="s">
         <v>656</v>
       </c>
@@ -48868,7 +48862,7 @@
         <v>359.92</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="219" t="s">
         <v>657</v>
       </c>
@@ -48918,27 +48912,27 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="219" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="219" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="219" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="219" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>640</v>
       </c>
@@ -48958,7 +48952,7 @@
       <c r="O28"/>
       <c r="P28"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>641</v>
       </c>
@@ -48978,7 +48972,7 @@
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>642</v>
       </c>
@@ -48998,7 +48992,7 @@
       <c r="O30"/>
       <c r="P30"/>
     </row>
-    <row r="31" spans="1:16" s="221" customFormat="1">
+    <row r="31" spans="1:16" s="221" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="220" t="s">
         <v>662</v>
       </c>
@@ -49018,7 +49012,7 @@
       <c r="O31" s="220"/>
       <c r="P31" s="220"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>644</v>
       </c>
@@ -49038,7 +49032,7 @@
       <c r="O32"/>
       <c r="P32"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
@@ -49056,7 +49050,7 @@
       <c r="O33"/>
       <c r="P33"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34"/>
       <c r="B34" t="s">
         <v>645</v>
@@ -49076,7 +49070,7 @@
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="223" t="s">
         <v>663</v>
       </c>
@@ -49126,7 +49120,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36"/>
@@ -49144,7 +49138,7 @@
       <c r="O36"/>
       <c r="P36"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>647</v>
       </c>
@@ -49194,7 +49188,7 @@
         <v>4803.3419999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38"/>
@@ -49212,7 +49206,7 @@
       <c r="O38"/>
       <c r="P38"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>664</v>
       </c>
@@ -49262,7 +49256,7 @@
         <v>275.14600000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>665</v>
       </c>
@@ -49312,7 +49306,7 @@
         <v>275.14600000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>666</v>
       </c>
@@ -49362,7 +49356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
@@ -49380,7 +49374,7 @@
       <c r="O42"/>
       <c r="P42"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>667</v>
       </c>
@@ -49430,7 +49424,7 @@
         <v>4528.1959999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>668</v>
       </c>
@@ -49480,7 +49474,7 @@
         <v>149.518</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>669</v>
       </c>
@@ -49530,7 +49524,7 @@
         <v>32.332999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>670</v>
       </c>
@@ -49580,7 +49574,7 @@
         <v>117.185</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>671</v>
       </c>
@@ -49630,7 +49624,7 @@
         <v>233.62799999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>672</v>
       </c>
@@ -49680,7 +49674,7 @@
         <v>1128.085</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>673</v>
       </c>
@@ -49730,7 +49724,7 @@
         <v>114.693</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>674</v>
       </c>
@@ -49780,7 +49774,7 @@
         <v>572.05999999999995</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>675</v>
       </c>
@@ -49830,7 +49824,7 @@
         <v>103.143</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>676</v>
       </c>
@@ -49880,7 +49874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>677</v>
       </c>
@@ -49930,7 +49924,7 @@
         <v>2213.002</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>678</v>
       </c>
@@ -49980,7 +49974,7 @@
         <v>14.067</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
@@ -49998,7 +49992,7 @@
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>679</v>
       </c>
@@ -50018,7 +50012,7 @@
       <c r="O56"/>
       <c r="P56"/>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>680</v>
       </c>
@@ -50038,7 +50032,7 @@
       <c r="O57"/>
       <c r="P57"/>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>659</v>
       </c>
@@ -50058,7 +50052,7 @@
       <c r="O58"/>
       <c r="P58"/>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>660</v>
       </c>
@@ -50078,7 +50072,7 @@
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
@@ -50096,32 +50090,32 @@
       <c r="O60"/>
       <c r="P60"/>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="219" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="219" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="219" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="65" spans="1:16" s="222" customFormat="1">
+    <row r="65" spans="1:16" s="222" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="222" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="219" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="223" t="s">
         <v>682</v>
       </c>
@@ -50129,7 +50123,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B69" s="219">
         <v>2005</v>
       </c>
@@ -50176,7 +50170,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="219" t="s">
         <v>647</v>
       </c>
@@ -50226,7 +50220,7 @@
         <v>2747.4409999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="219" t="s">
         <v>664</v>
       </c>
@@ -50276,7 +50270,7 @@
         <v>2465.4540000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="219" t="s">
         <v>665</v>
       </c>
@@ -50326,7 +50320,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="219" t="s">
         <v>666</v>
       </c>
@@ -50376,7 +50370,7 @@
         <v>2465.319</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="219" t="s">
         <v>683</v>
       </c>
@@ -50426,7 +50420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="219" t="s">
         <v>667</v>
       </c>
@@ -50476,7 +50470,7 @@
         <v>281.98700000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="219" t="s">
         <v>668</v>
       </c>
@@ -50526,7 +50520,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="219" t="s">
         <v>669</v>
       </c>
@@ -50576,7 +50570,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="219" t="s">
         <v>670</v>
       </c>
@@ -50626,7 +50620,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="219" t="s">
         <v>671</v>
       </c>
@@ -50676,7 +50670,7 @@
         <v>1.3959999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="219" t="s">
         <v>672</v>
       </c>
@@ -50726,7 +50720,7 @@
         <v>64.677999999999997</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="219" t="s">
         <v>673</v>
       </c>
@@ -50776,7 +50770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="219" t="s">
         <v>674</v>
       </c>
@@ -50826,7 +50820,7 @@
         <v>27.128</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="219" t="s">
         <v>675</v>
       </c>
@@ -50876,7 +50870,7 @@
         <v>168.52099999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="219" t="s">
         <v>676</v>
       </c>
@@ -50926,7 +50920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="219" t="s">
         <v>677</v>
       </c>
@@ -50976,7 +50970,7 @@
         <v>1.403</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="219" t="s">
         <v>678</v>
       </c>
@@ -51026,17 +51020,17 @@
         <v>18.762</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="219" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="219" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="219" t="s">
         <v>660</v>
       </c>
@@ -51052,43 +51046,43 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:AA49"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" style="219" customWidth="1"/>
-    <col min="2" max="16384" width="10.85546875" style="219"/>
+    <col min="1" max="1" width="40.33203125" style="219" customWidth="1"/>
+    <col min="2" max="16384" width="10.88671875" style="219"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="219" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="219" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="219" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="219" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="219" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="219" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="51">
+    <row r="9" spans="1:27" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B9" s="225" t="s">
         <v>687</v>
       </c>
@@ -51168,7 +51162,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="226" t="s">
         <v>712</v>
       </c>
@@ -51251,7 +51245,7 @@
         <v>6332.8119999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="219" t="s">
         <v>713</v>
       </c>
@@ -51301,7 +51295,7 @@
         <v>684.327</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="226" t="s">
         <v>714</v>
       </c>
@@ -51364,7 +51358,7 @@
         <v>4803.3419999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="219" t="s">
         <v>715</v>
       </c>
@@ -51420,7 +51414,7 @@
         <v>-37.838000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="219" t="s">
         <v>716</v>
       </c>
@@ -51503,7 +51497,7 @@
         <v>11782.641</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="226" t="s">
         <v>717</v>
       </c>
@@ -51568,7 +51562,7 @@
         <v>-2747.44</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="219" t="s">
         <v>718</v>
       </c>
@@ -51597,7 +51591,7 @@
         <v>-224.148</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="219" t="s">
         <v>719</v>
       </c>
@@ -51638,7 +51632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="219" t="s">
         <v>720</v>
       </c>
@@ -51721,7 +51715,7 @@
         <v>8811.0529999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="219" t="s">
         <v>721</v>
       </c>
@@ -51804,7 +51798,7 @@
         <v>-1936.570154</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="219" t="s">
         <v>722</v>
       </c>
@@ -51830,7 +51824,7 @@
         <v>-9.2110000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="219" t="s">
         <v>723</v>
       </c>
@@ -51880,7 +51874,7 @@
         <v>-115.21299999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="219" t="s">
         <v>724</v>
       </c>
@@ -51927,7 +51921,7 @@
         <v>-116.233</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="219" t="s">
         <v>725</v>
       </c>
@@ -51974,7 +51968,7 @@
         <v>-895.28700000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="219" t="s">
         <v>726</v>
       </c>
@@ -52003,7 +51997,7 @@
         <v>-281.98700000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="219" t="s">
         <v>727</v>
       </c>
@@ -52059,7 +52053,7 @@
         <v>-440.82900000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="219" t="s">
         <v>728</v>
       </c>
@@ -52097,7 +52091,7 @@
         <v>-77.809154000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="219" t="s">
         <v>729</v>
       </c>
@@ -52153,7 +52147,7 @@
         <v>-1146.575</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="219" t="s">
         <v>730</v>
       </c>
@@ -52179,7 +52173,7 @@
         <v>-0.72899999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="219" t="s">
         <v>731</v>
       </c>
@@ -52205,7 +52199,7 @@
         <v>-511.82799999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="219" t="s">
         <v>732</v>
       </c>
@@ -52285,7 +52279,7 @@
         <v>-192.35598200000001</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="219" t="s">
         <v>733</v>
       </c>
@@ -52308,7 +52302,7 @@
         <v>-198.381</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="219" t="s">
         <v>734</v>
       </c>
@@ -52370,7 +52364,7 @@
         <v>4851.5690000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="219" t="s">
         <v>735</v>
       </c>
@@ -52411,7 +52405,7 @@
         <v>90.594999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="219" t="s">
         <v>736</v>
       </c>
@@ -52440,7 +52434,7 @@
         <v>47.935000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="219" t="s">
         <v>737</v>
       </c>
@@ -52481,7 +52475,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="219" t="s">
         <v>738</v>
       </c>
@@ -52537,7 +52531,7 @@
         <v>4760.9750000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="219" t="s">
         <v>739</v>
       </c>
@@ -52578,7 +52572,7 @@
         <v>952.58699999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="219" t="s">
         <v>740</v>
       </c>
@@ -52613,7 +52607,7 @@
         <v>2058.6860000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="219" t="s">
         <v>741</v>
       </c>
@@ -52645,7 +52639,7 @@
         <v>191.89500000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="219" t="s">
         <v>742</v>
       </c>
@@ -52698,7 +52692,7 @@
         <v>1557.81</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="226" t="s">
         <v>743</v>
       </c>
@@ -52755,32 +52749,32 @@
         <v>3702.0030000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="219" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="45" spans="1:27">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="219" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="219" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="219" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="219" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="219" t="s">
         <v>661</v>
       </c>
@@ -52791,21 +52785,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -52949,14 +52928,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887C0CA8-FB8F-4A9B-A052-30CE6D56B689}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536B017B-1DE8-4611-A06E-7793E6FBD9EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{414FBA7A-6D38-406A-A36F-9CBA3CCB13D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{414FBA7A-6D38-406A-A36F-9CBA3CCB13D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536B017B-1DE8-4611-A06E-7793E6FBD9EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887C0CA8-FB8F-4A9B-A052-30CE6D56B689}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>